--- a/ميدسيرفس.xlsx
+++ b/ميدسيرفس.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD30514-6658-4591-8A70-BB4B79F9CF4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E47913-00B2-4B78-BD59-9835E74C7CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D788D8F7-2544-4C2F-9B89-70931910278C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="205">
   <si>
     <t>الرقم</t>
   </si>
@@ -633,6 +633,24 @@
   </si>
   <si>
     <t>علاءالدين الحسنات</t>
+  </si>
+  <si>
+    <t>12893*230877*0</t>
+  </si>
+  <si>
+    <t>اياس علي نعيمي</t>
+  </si>
+  <si>
+    <t>12885*324724*329244</t>
+  </si>
+  <si>
+    <t>هديل سليمان صبيح الجازي</t>
+  </si>
+  <si>
+    <t>12893*230850*232146</t>
+  </si>
+  <si>
+    <t>ندا الحسنات</t>
   </si>
 </sst>
 </file>
@@ -707,31 +725,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="12">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color indexed="9"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor indexed="17"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
@@ -901,6 +894,31 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="9"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor indexed="17"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -915,26 +933,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}" name="Table1" displayName="Table1" ref="A1:L174" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:L174" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}" name="Table1" displayName="Table1" ref="A1:L180" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A1:L180" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L174">
     <sortCondition ref="F1:F174"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{60C6F871-C16F-4E0C-BCFA-8355ABD999C9}" name="الرقم" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{16663A49-EAEA-4D0C-AEE4-F16F12092E0B}" name="رقم الموظف /رقم البطاقة" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{E695BC9D-90B5-4017-835E-DE39F27EC4B5}" name="اسم المريض" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{4FA0F61B-0974-4290-8AF9-64F3425CF95F}" name="رقم النموذج" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{FA7C7B11-59CD-43FE-8614-AE77C814F7B1}" name="نوع المستفيد" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{A5C7FB1D-369A-430A-90FD-DECEB437BB07}" name="تاريخ البيع" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{A0C6C549-4E6F-40C8-8B90-0D7D85B722AF}" name="قيمة الفاتورة" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{FE5B0B26-736F-4D13-A599-E33B398493F1}" name="قيمة المشاركة" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{BC1FF825-92ED-4149-A1D2-B9B13F698346}" name="صافي القيمة" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{856C6145-2E1C-4B6E-9442-8F25AAAF88C3}" name="القيمة المطلوبة" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{60C6F871-C16F-4E0C-BCFA-8355ABD999C9}" name="الرقم" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{16663A49-EAEA-4D0C-AEE4-F16F12092E0B}" name="رقم الموظف /رقم البطاقة" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{E695BC9D-90B5-4017-835E-DE39F27EC4B5}" name="اسم المريض" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{4FA0F61B-0974-4290-8AF9-64F3425CF95F}" name="رقم النموذج" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{FA7C7B11-59CD-43FE-8614-AE77C814F7B1}" name="نوع المستفيد" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{A5C7FB1D-369A-430A-90FD-DECEB437BB07}" name="تاريخ البيع" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{A0C6C549-4E6F-40C8-8B90-0D7D85B722AF}" name="قيمة الفاتورة" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{FE5B0B26-736F-4D13-A599-E33B398493F1}" name="قيمة المشاركة" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{BC1FF825-92ED-4149-A1D2-B9B13F698346}" name="صافي القيمة" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{856C6145-2E1C-4B6E-9442-8F25AAAF88C3}" name="القيمة المطلوبة" dataDxfId="1">
       <calculatedColumnFormula>G2*0.94-H2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="11" xr3:uid="{93671F58-AEBB-42C2-8ECB-4A20CA480AFD}" name="المدفوع"/>
-    <tableColumn id="12" xr3:uid="{3CB96BCB-F76A-4AB9-8336-BDA8FF662F9F}" name="المتبقي" dataDxfId="1">
+    <tableColumn id="12" xr3:uid="{3CB96BCB-F76A-4AB9-8336-BDA8FF662F9F}" name="المتبقي" dataDxfId="0">
       <calculatedColumnFormula>J2-K2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1259,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA9FC926-0A16-40E2-AC7F-885A2855875E}">
-  <dimension ref="A1:L174"/>
+  <dimension ref="A1:L180"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -1343,11 +1361,11 @@
         <v>21.26</v>
       </c>
       <c r="J2" s="6">
-        <f>G2*0.94-H2</f>
+        <f t="shared" ref="J2:J33" si="0">G2*0.94-H2</f>
         <v>19.984400000000001</v>
       </c>
       <c r="L2" s="6">
-        <f>J2-K2</f>
+        <f t="shared" ref="L2:L33" si="1">J2-K2</f>
         <v>19.984400000000001</v>
       </c>
     </row>
@@ -1380,11 +1398,11 @@
         <v>26.36</v>
       </c>
       <c r="J3" s="6">
-        <f>G3*0.94-H3</f>
+        <f t="shared" si="0"/>
         <v>24.778399999999998</v>
       </c>
       <c r="L3" s="6">
-        <f>J3-K3</f>
+        <f t="shared" si="1"/>
         <v>24.778399999999998</v>
       </c>
     </row>
@@ -1417,11 +1435,11 @@
         <v>43.42</v>
       </c>
       <c r="J4" s="6">
-        <f>G4*0.94-H4</f>
+        <f t="shared" si="0"/>
         <v>40.814799999999998</v>
       </c>
       <c r="L4" s="6">
-        <f>J4-K4</f>
+        <f t="shared" si="1"/>
         <v>40.814799999999998</v>
       </c>
     </row>
@@ -1454,11 +1472,11 @@
         <v>3.64</v>
       </c>
       <c r="J5" s="6">
-        <f>G5*0.94-H5</f>
+        <f t="shared" si="0"/>
         <v>3.4215999999999998</v>
       </c>
       <c r="L5" s="6">
-        <f>J5-K5</f>
+        <f t="shared" si="1"/>
         <v>3.4215999999999998</v>
       </c>
     </row>
@@ -1491,11 +1509,11 @@
         <v>3.84</v>
       </c>
       <c r="J6" s="6">
-        <f>G6*0.94-H6</f>
+        <f t="shared" si="0"/>
         <v>3.6095999999999995</v>
       </c>
       <c r="L6" s="6">
-        <f>J6-K6</f>
+        <f t="shared" si="1"/>
         <v>3.6095999999999995</v>
       </c>
     </row>
@@ -1528,11 +1546,11 @@
         <v>28.92</v>
       </c>
       <c r="J7" s="6">
-        <f>G7*0.94-H7</f>
+        <f t="shared" si="0"/>
         <v>27.184799999999999</v>
       </c>
       <c r="L7" s="6">
-        <f>J7-K7</f>
+        <f t="shared" si="1"/>
         <v>27.184799999999999</v>
       </c>
     </row>
@@ -1565,11 +1583,11 @@
         <v>12.303000000000001</v>
       </c>
       <c r="J8" s="6">
-        <f>G8*0.94-H8</f>
+        <f t="shared" si="0"/>
         <v>11.482799999999997</v>
       </c>
       <c r="L8" s="6">
-        <f>J8-K8</f>
+        <f t="shared" si="1"/>
         <v>11.482799999999997</v>
       </c>
     </row>
@@ -1602,11 +1620,11 @@
         <v>22.599</v>
       </c>
       <c r="J9" s="6">
-        <f>G9*0.94-H9</f>
+        <f t="shared" si="0"/>
         <v>21.092399999999998</v>
       </c>
       <c r="L9" s="6">
-        <f>J9-K9</f>
+        <f t="shared" si="1"/>
         <v>21.092399999999998</v>
       </c>
     </row>
@@ -1639,11 +1657,11 @@
         <v>22.86</v>
       </c>
       <c r="J10" s="6">
-        <f>G10*0.94-H10</f>
+        <f t="shared" si="0"/>
         <v>21.335999999999999</v>
       </c>
       <c r="L10" s="6">
-        <f>J10-K10</f>
+        <f t="shared" si="1"/>
         <v>21.335999999999999</v>
       </c>
     </row>
@@ -1676,11 +1694,11 @@
         <v>11.936</v>
       </c>
       <c r="J11" s="6">
-        <f>G11*0.94-H11</f>
+        <f t="shared" si="0"/>
         <v>11.040799999999999</v>
       </c>
       <c r="L11" s="6">
-        <f>J11-K11</f>
+        <f t="shared" si="1"/>
         <v>11.040799999999999</v>
       </c>
     </row>
@@ -1713,11 +1731,11 @@
         <v>10.584</v>
       </c>
       <c r="J12" s="6">
-        <f>G12*0.94-H12</f>
+        <f t="shared" si="0"/>
         <v>9.7901999999999987</v>
       </c>
       <c r="L12" s="6">
-        <f>J12-K12</f>
+        <f t="shared" si="1"/>
         <v>9.7901999999999987</v>
       </c>
     </row>
@@ -1750,11 +1768,11 @@
         <v>42.944000000000003</v>
       </c>
       <c r="J13" s="6">
-        <f>G13*0.94-H13</f>
+        <f t="shared" si="0"/>
         <v>39.723199999999991</v>
       </c>
       <c r="L13" s="6">
-        <f>J13-K13</f>
+        <f t="shared" si="1"/>
         <v>39.723199999999991</v>
       </c>
     </row>
@@ -1787,11 +1805,11 @@
         <v>59.94</v>
       </c>
       <c r="J14" s="6">
-        <f>G14*0.94-H14</f>
+        <f t="shared" si="0"/>
         <v>55.943999999999988</v>
       </c>
       <c r="L14" s="6">
-        <f>J14-K14</f>
+        <f t="shared" si="1"/>
         <v>55.943999999999988</v>
       </c>
     </row>
@@ -1824,11 +1842,11 @@
         <v>24.78</v>
       </c>
       <c r="J15" s="6">
-        <f>G15*0.94-H15</f>
+        <f t="shared" si="0"/>
         <v>23.293199999999999</v>
       </c>
       <c r="L15" s="6">
-        <f>J15-K15</f>
+        <f t="shared" si="1"/>
         <v>23.293199999999999</v>
       </c>
     </row>
@@ -1861,11 +1879,11 @@
         <v>23.067</v>
       </c>
       <c r="J16" s="6">
-        <f>G16*0.94-H16</f>
+        <f t="shared" si="0"/>
         <v>21.529199999999999</v>
       </c>
       <c r="L16" s="6">
-        <f>J16-K16</f>
+        <f t="shared" si="1"/>
         <v>21.529199999999999</v>
       </c>
     </row>
@@ -1898,11 +1916,11 @@
         <v>33.093000000000004</v>
       </c>
       <c r="J17" s="6">
-        <f>G17*0.94-H17</f>
+        <f t="shared" si="0"/>
         <v>30.886800000000001</v>
       </c>
       <c r="L17" s="6">
-        <f>J17-K17</f>
+        <f t="shared" si="1"/>
         <v>30.886800000000001</v>
       </c>
     </row>
@@ -1935,11 +1953,11 @@
         <v>35.918999999999997</v>
       </c>
       <c r="J18" s="6">
-        <f>G18*0.94-H18</f>
+        <f t="shared" si="0"/>
         <v>33.524399999999993</v>
       </c>
       <c r="L18" s="6">
-        <f>J18-K18</f>
+        <f t="shared" si="1"/>
         <v>33.524399999999993</v>
       </c>
     </row>
@@ -1972,11 +1990,11 @@
         <v>12.645</v>
       </c>
       <c r="J19" s="6">
-        <f>G19*0.94-H19</f>
+        <f t="shared" si="0"/>
         <v>11.802000000000001</v>
       </c>
       <c r="L19" s="6">
-        <f>J19-K19</f>
+        <f t="shared" si="1"/>
         <v>11.802000000000001</v>
       </c>
     </row>
@@ -2009,11 +2027,11 @@
         <v>17.721</v>
       </c>
       <c r="J20" s="6">
-        <f>G20*0.94-H20</f>
+        <f t="shared" si="0"/>
         <v>16.5396</v>
       </c>
       <c r="L20" s="6">
-        <f>J20-K20</f>
+        <f t="shared" si="1"/>
         <v>16.5396</v>
       </c>
     </row>
@@ -2046,11 +2064,11 @@
         <v>29.061</v>
       </c>
       <c r="J21" s="6">
-        <f>G21*0.94-H21</f>
+        <f t="shared" si="0"/>
         <v>27.1236</v>
       </c>
       <c r="L21" s="6">
-        <f>J21-K21</f>
+        <f t="shared" si="1"/>
         <v>27.1236</v>
       </c>
     </row>
@@ -2083,11 +2101,11 @@
         <v>38.780999999999999</v>
       </c>
       <c r="J22" s="6">
-        <f>G22*0.94-H22</f>
+        <f t="shared" si="0"/>
         <v>36.195600000000006</v>
       </c>
       <c r="L22" s="6">
-        <f>J22-K22</f>
+        <f t="shared" si="1"/>
         <v>36.195600000000006</v>
       </c>
     </row>
@@ -2120,11 +2138,11 @@
         <v>13.941000000000001</v>
       </c>
       <c r="J23" s="6">
-        <f>G23*0.94-H23</f>
+        <f t="shared" si="0"/>
         <v>13.0116</v>
       </c>
       <c r="L23" s="6">
-        <f>J23-K23</f>
+        <f t="shared" si="1"/>
         <v>13.0116</v>
       </c>
     </row>
@@ -2157,11 +2175,11 @@
         <v>15.561</v>
       </c>
       <c r="J24" s="6">
-        <f>G24*0.94-H24</f>
+        <f t="shared" si="0"/>
         <v>14.523599999999998</v>
       </c>
       <c r="L24" s="6">
-        <f>J24-K24</f>
+        <f t="shared" si="1"/>
         <v>14.523599999999998</v>
       </c>
     </row>
@@ -2194,11 +2212,11 @@
         <v>10.853999999999999</v>
       </c>
       <c r="J25" s="6">
-        <f>G25*0.94-H25</f>
+        <f t="shared" si="0"/>
         <v>10.1304</v>
       </c>
       <c r="L25" s="6">
-        <f>J25-K25</f>
+        <f t="shared" si="1"/>
         <v>10.1304</v>
       </c>
     </row>
@@ -2231,11 +2249,11 @@
         <v>7.4790000000000001</v>
       </c>
       <c r="J26" s="6">
-        <f>G26*0.94-H26</f>
+        <f t="shared" si="0"/>
         <v>6.9803999999999995</v>
       </c>
       <c r="L26" s="6">
-        <f>J26-K26</f>
+        <f t="shared" si="1"/>
         <v>6.9803999999999995</v>
       </c>
     </row>
@@ -2268,11 +2286,11 @@
         <v>14.949</v>
       </c>
       <c r="J27" s="6">
-        <f>G27*0.94-H27</f>
+        <f t="shared" si="0"/>
         <v>13.952399999999999</v>
       </c>
       <c r="L27" s="6">
-        <f>J27-K27</f>
+        <f t="shared" si="1"/>
         <v>13.952399999999999</v>
       </c>
     </row>
@@ -2305,11 +2323,11 @@
         <v>29.817</v>
       </c>
       <c r="J28" s="6">
-        <f>G28*0.94-H28</f>
+        <f t="shared" si="0"/>
         <v>27.8292</v>
       </c>
       <c r="L28" s="6">
-        <f>J28-K28</f>
+        <f t="shared" si="1"/>
         <v>27.8292</v>
       </c>
     </row>
@@ -2342,12 +2360,12 @@
         <v>21.21</v>
       </c>
       <c r="J29" s="6">
-        <f>G29*0.94-H29</f>
+        <f t="shared" si="0"/>
         <v>19.9374</v>
       </c>
       <c r="K29"/>
       <c r="L29" s="6">
-        <f>J29-K29</f>
+        <f t="shared" si="1"/>
         <v>19.9374</v>
       </c>
     </row>
@@ -2380,11 +2398,11 @@
         <v>15.18</v>
       </c>
       <c r="J30" s="6">
-        <f>G30*0.94-H30</f>
+        <f t="shared" si="0"/>
         <v>14.2692</v>
       </c>
       <c r="L30" s="6">
-        <f>J30-K30</f>
+        <f t="shared" si="1"/>
         <v>14.2692</v>
       </c>
     </row>
@@ -2417,11 +2435,11 @@
         <v>13.103999999999999</v>
       </c>
       <c r="J31" s="6">
-        <f>G31*0.94-H31</f>
+        <f t="shared" si="0"/>
         <v>12.230399999999999</v>
       </c>
       <c r="L31" s="6">
-        <f>J31-K31</f>
+        <f t="shared" si="1"/>
         <v>12.230399999999999</v>
       </c>
     </row>
@@ -2454,11 +2472,11 @@
         <v>26.408000000000001</v>
       </c>
       <c r="J32" s="6">
-        <f>G32*0.94-H32</f>
+        <f t="shared" si="0"/>
         <v>24.427399999999995</v>
       </c>
       <c r="L32" s="6">
-        <f>J32-K32</f>
+        <f t="shared" si="1"/>
         <v>24.427399999999995</v>
       </c>
     </row>
@@ -2491,11 +2509,11 @@
         <v>37.790999999999997</v>
       </c>
       <c r="J33" s="6">
-        <f>G33*0.94-H33</f>
+        <f t="shared" si="0"/>
         <v>35.271599999999999</v>
       </c>
       <c r="L33" s="6">
-        <f>J33-K33</f>
+        <f t="shared" si="1"/>
         <v>35.271599999999999</v>
       </c>
     </row>
@@ -2528,11 +2546,11 @@
         <v>22.635000000000002</v>
       </c>
       <c r="J34" s="6">
-        <f>G34*0.94-H34</f>
+        <f t="shared" ref="J34:J65" si="2">G34*0.94-H34</f>
         <v>21.125999999999998</v>
       </c>
       <c r="L34" s="6">
-        <f>J34-K34</f>
+        <f t="shared" ref="L34:L65" si="3">J34-K34</f>
         <v>21.125999999999998</v>
       </c>
     </row>
@@ -2565,11 +2583,11 @@
         <v>25.443000000000001</v>
       </c>
       <c r="J35" s="6">
-        <f>G35*0.94-H35</f>
+        <f t="shared" si="2"/>
         <v>23.7468</v>
       </c>
       <c r="L35" s="6">
-        <f>J35-K35</f>
+        <f t="shared" si="3"/>
         <v>23.7468</v>
       </c>
     </row>
@@ -2602,11 +2620,11 @@
         <v>27.54</v>
       </c>
       <c r="J36" s="6">
-        <f>G36*0.94-H36</f>
+        <f t="shared" si="2"/>
         <v>25.887599999999999</v>
       </c>
       <c r="L36" s="6">
-        <f>J36-K36</f>
+        <f t="shared" si="3"/>
         <v>25.887599999999999</v>
       </c>
     </row>
@@ -2639,11 +2657,11 @@
         <v>17.7</v>
       </c>
       <c r="J37" s="6">
-        <f>G37*0.94-H37</f>
+        <f t="shared" si="2"/>
         <v>16.637999999999998</v>
       </c>
       <c r="L37" s="6">
-        <f>J37-K37</f>
+        <f t="shared" si="3"/>
         <v>16.637999999999998</v>
       </c>
     </row>
@@ -2676,11 +2694,11 @@
         <v>50.31</v>
       </c>
       <c r="J38" s="6">
-        <f>G38*0.94-H38</f>
+        <f t="shared" si="2"/>
         <v>47.291400000000003</v>
       </c>
       <c r="L38" s="6">
-        <f>J38-K38</f>
+        <f t="shared" si="3"/>
         <v>47.291400000000003</v>
       </c>
     </row>
@@ -2713,11 +2731,11 @@
         <v>39.213000000000001</v>
       </c>
       <c r="J39" s="6">
-        <f>G39*0.94-H39</f>
+        <f t="shared" si="2"/>
         <v>36.598799999999997</v>
       </c>
       <c r="L39" s="6">
-        <f>J39-K39</f>
+        <f t="shared" si="3"/>
         <v>36.598799999999997</v>
       </c>
     </row>
@@ -2750,11 +2768,11 @@
         <v>7.3529999999999998</v>
       </c>
       <c r="J40" s="6">
-        <f>G40*0.94-H40</f>
+        <f t="shared" si="2"/>
         <v>6.8627999999999991</v>
       </c>
       <c r="L40" s="6">
-        <f>J40-K40</f>
+        <f t="shared" si="3"/>
         <v>6.8627999999999991</v>
       </c>
     </row>
@@ -2787,11 +2805,11 @@
         <v>37.584000000000003</v>
       </c>
       <c r="J41" s="6">
-        <f>G41*0.94-H41</f>
+        <f t="shared" si="2"/>
         <v>35.078399999999995</v>
       </c>
       <c r="L41" s="6">
-        <f>J41-K41</f>
+        <f t="shared" si="3"/>
         <v>35.078399999999995</v>
       </c>
     </row>
@@ -2824,11 +2842,11 @@
         <v>15.12</v>
       </c>
       <c r="J42" s="6">
-        <f>G42*0.94-H42</f>
+        <f t="shared" si="2"/>
         <v>14.112</v>
       </c>
       <c r="L42" s="6">
-        <f>J42-K42</f>
+        <f t="shared" si="3"/>
         <v>14.112</v>
       </c>
     </row>
@@ -2861,12 +2879,12 @@
         <v>2.496</v>
       </c>
       <c r="J43" s="6">
-        <f>G43*0.94-H43</f>
+        <f t="shared" si="2"/>
         <v>2.3087999999999997</v>
       </c>
       <c r="K43"/>
       <c r="L43" s="6">
-        <f>J43-K43</f>
+        <f t="shared" si="3"/>
         <v>2.3087999999999997</v>
       </c>
     </row>
@@ -2899,11 +2917,11 @@
         <v>7.569</v>
       </c>
       <c r="J44" s="6">
-        <f>G44*0.94-H44</f>
+        <f t="shared" si="2"/>
         <v>7.0643999999999991</v>
       </c>
       <c r="L44" s="6">
-        <f>J44-K44</f>
+        <f t="shared" si="3"/>
         <v>7.0643999999999991</v>
       </c>
     </row>
@@ -2936,11 +2954,11 @@
         <v>52.25</v>
       </c>
       <c r="J45" s="6">
-        <f>G45*0.94-H45</f>
+        <f t="shared" si="2"/>
         <v>49.114999999999995</v>
       </c>
       <c r="L45" s="6">
-        <f>J45-K45</f>
+        <f t="shared" si="3"/>
         <v>49.114999999999995</v>
       </c>
     </row>
@@ -2973,11 +2991,11 @@
         <v>11.952</v>
       </c>
       <c r="J46" s="6">
-        <f>G46*0.94-H46</f>
+        <f t="shared" si="2"/>
         <v>11.155199999999999</v>
       </c>
       <c r="L46" s="6">
-        <f>J46-K46</f>
+        <f t="shared" si="3"/>
         <v>11.155199999999999</v>
       </c>
     </row>
@@ -3010,11 +3028,11 @@
         <v>23.904</v>
       </c>
       <c r="J47" s="6">
-        <f>G47*0.94-H47</f>
+        <f t="shared" si="2"/>
         <v>22.310399999999998</v>
       </c>
       <c r="L47" s="6">
-        <f>J47-K47</f>
+        <f t="shared" si="3"/>
         <v>22.310399999999998</v>
       </c>
     </row>
@@ -3047,12 +3065,12 @@
         <v>19.791</v>
       </c>
       <c r="J48" s="6">
-        <f>G48*0.94-H48</f>
+        <f t="shared" si="2"/>
         <v>18.471599999999995</v>
       </c>
       <c r="K48"/>
       <c r="L48" s="6">
-        <f>J48-K48</f>
+        <f t="shared" si="3"/>
         <v>18.471599999999995</v>
       </c>
     </row>
@@ -3085,11 +3103,11 @@
         <v>21.969000000000001</v>
       </c>
       <c r="J49" s="6">
-        <f>G49*0.94-H49</f>
+        <f t="shared" si="2"/>
         <v>20.5044</v>
       </c>
       <c r="L49" s="6">
-        <f>J49-K49</f>
+        <f t="shared" si="3"/>
         <v>20.5044</v>
       </c>
     </row>
@@ -3122,11 +3140,11 @@
         <v>21.78</v>
       </c>
       <c r="J50" s="6">
-        <f>G50*0.94-H50</f>
+        <f t="shared" si="2"/>
         <v>20.327999999999996</v>
       </c>
       <c r="L50" s="6">
-        <f>J50-K50</f>
+        <f t="shared" si="3"/>
         <v>20.327999999999996</v>
       </c>
     </row>
@@ -3159,11 +3177,11 @@
         <v>19.818000000000001</v>
       </c>
       <c r="J51" s="6">
-        <f>G51*0.94-H51</f>
+        <f t="shared" si="2"/>
         <v>18.4968</v>
       </c>
       <c r="L51" s="6">
-        <f>J51-K51</f>
+        <f t="shared" si="3"/>
         <v>18.4968</v>
       </c>
     </row>
@@ -3196,11 +3214,11 @@
         <v>19.305</v>
       </c>
       <c r="J52" s="6">
-        <f>G52*0.94-H52</f>
+        <f t="shared" si="2"/>
         <v>18.017999999999997</v>
       </c>
       <c r="L52" s="6">
-        <f>J52-K52</f>
+        <f t="shared" si="3"/>
         <v>18.017999999999997</v>
       </c>
     </row>
@@ -3233,11 +3251,11 @@
         <v>12.968999999999999</v>
       </c>
       <c r="J53" s="6">
-        <f>G53*0.94-H53</f>
+        <f t="shared" si="2"/>
         <v>12.104399999999998</v>
       </c>
       <c r="L53" s="6">
-        <f>J53-K53</f>
+        <f t="shared" si="3"/>
         <v>12.104399999999998</v>
       </c>
     </row>
@@ -3270,11 +3288,11 @@
         <v>28.116</v>
       </c>
       <c r="J54" s="6">
-        <f>G54*0.94-H54</f>
+        <f t="shared" si="2"/>
         <v>26.241599999999998</v>
       </c>
       <c r="L54" s="6">
-        <f>J54-K54</f>
+        <f t="shared" si="3"/>
         <v>26.241599999999998</v>
       </c>
     </row>
@@ -3307,11 +3325,11 @@
         <v>22.274999999999999</v>
       </c>
       <c r="J55" s="6">
-        <f>G55*0.94-H55</f>
+        <f t="shared" si="2"/>
         <v>20.789999999999996</v>
       </c>
       <c r="L55" s="6">
-        <f>J55-K55</f>
+        <f t="shared" si="3"/>
         <v>20.789999999999996</v>
       </c>
     </row>
@@ -3344,11 +3362,11 @@
         <v>39.258000000000003</v>
       </c>
       <c r="J56" s="6">
-        <f>G56*0.94-H56</f>
+        <f t="shared" si="2"/>
         <v>36.640799999999992</v>
       </c>
       <c r="L56" s="6">
-        <f>J56-K56</f>
+        <f t="shared" si="3"/>
         <v>36.640799999999992</v>
       </c>
     </row>
@@ -3381,11 +3399,11 @@
         <v>23.544</v>
       </c>
       <c r="J57" s="6">
-        <f>G57*0.94-H57</f>
+        <f t="shared" si="2"/>
         <v>21.974399999999999</v>
       </c>
       <c r="L57" s="6">
-        <f>J57-K57</f>
+        <f t="shared" si="3"/>
         <v>21.974399999999999</v>
       </c>
     </row>
@@ -3418,11 +3436,11 @@
         <v>28.277999999999999</v>
       </c>
       <c r="J58" s="6">
-        <f>G58*0.94-H58</f>
+        <f t="shared" si="2"/>
         <v>26.392800000000001</v>
       </c>
       <c r="L58" s="6">
-        <f>J58-K58</f>
+        <f t="shared" si="3"/>
         <v>26.392800000000001</v>
       </c>
     </row>
@@ -3455,11 +3473,11 @@
         <v>20.331</v>
       </c>
       <c r="J59" s="6">
-        <f>G59*0.94-H59</f>
+        <f t="shared" si="2"/>
         <v>18.9756</v>
       </c>
       <c r="L59" s="6">
-        <f>J59-K59</f>
+        <f t="shared" si="3"/>
         <v>18.9756</v>
       </c>
     </row>
@@ -3492,11 +3510,11 @@
         <v>54.161999999999999</v>
       </c>
       <c r="J60" s="6">
-        <f>G60*0.94-H60</f>
+        <f t="shared" si="2"/>
         <v>50.551199999999994</v>
       </c>
       <c r="L60" s="6">
-        <f>J60-K60</f>
+        <f t="shared" si="3"/>
         <v>50.551199999999994</v>
       </c>
     </row>
@@ -3529,11 +3547,11 @@
         <v>29.103999999999999</v>
       </c>
       <c r="J61" s="6">
-        <f>G61*0.94-H61</f>
+        <f t="shared" si="2"/>
         <v>26.921200000000002</v>
       </c>
       <c r="L61" s="6">
-        <f>J61-K61</f>
+        <f t="shared" si="3"/>
         <v>26.921200000000002</v>
       </c>
     </row>
@@ -3566,11 +3584,11 @@
         <v>30.15</v>
       </c>
       <c r="J62" s="6">
-        <f>G62*0.94-H62</f>
+        <f t="shared" si="2"/>
         <v>28.139999999999997</v>
       </c>
       <c r="L62" s="6">
-        <f>J62-K62</f>
+        <f t="shared" si="3"/>
         <v>28.139999999999997</v>
       </c>
     </row>
@@ -3603,11 +3621,11 @@
         <v>10.54</v>
       </c>
       <c r="J63" s="6">
-        <f>G63*0.94-H63</f>
+        <f t="shared" si="2"/>
         <v>9.9075999999999986</v>
       </c>
       <c r="L63" s="6">
-        <f>J63-K63</f>
+        <f t="shared" si="3"/>
         <v>9.9075999999999986</v>
       </c>
     </row>
@@ -3640,11 +3658,11 @@
         <v>34.96</v>
       </c>
       <c r="J64" s="6">
-        <f>G64*0.94-H64</f>
+        <f t="shared" si="2"/>
         <v>32.862400000000001</v>
       </c>
       <c r="L64" s="6">
-        <f>J64-K64</f>
+        <f t="shared" si="3"/>
         <v>32.862400000000001</v>
       </c>
     </row>
@@ -3677,11 +3695,11 @@
         <v>48.64</v>
       </c>
       <c r="J65" s="6">
-        <f>G65*0.94-H65</f>
+        <f t="shared" si="2"/>
         <v>45.721599999999995</v>
       </c>
       <c r="L65" s="6">
-        <f>J65-K65</f>
+        <f t="shared" si="3"/>
         <v>45.721599999999995</v>
       </c>
     </row>
@@ -3714,11 +3732,11 @@
         <v>27.297000000000001</v>
       </c>
       <c r="J66" s="6">
-        <f>G66*0.94-H66</f>
+        <f t="shared" ref="J66:J97" si="4">G66*0.94-H66</f>
         <v>25.477199999999996</v>
       </c>
       <c r="L66" s="6">
-        <f>J66-K66</f>
+        <f t="shared" ref="L66:L97" si="5">J66-K66</f>
         <v>25.477199999999996</v>
       </c>
     </row>
@@ -3751,11 +3769,11 @@
         <v>48.851999999999997</v>
       </c>
       <c r="J67" s="6">
-        <f>G67*0.94-H67</f>
+        <f t="shared" si="4"/>
         <v>45.595199999999998</v>
       </c>
       <c r="L67" s="6">
-        <f>J67-K67</f>
+        <f t="shared" si="5"/>
         <v>45.595199999999998</v>
       </c>
     </row>
@@ -3788,11 +3806,11 @@
         <v>8.9009999999999998</v>
       </c>
       <c r="J68" s="6">
-        <f>G68*0.94-H68</f>
+        <f t="shared" si="4"/>
         <v>8.307599999999999</v>
       </c>
       <c r="L68" s="6">
-        <f>J68-K68</f>
+        <f t="shared" si="5"/>
         <v>8.307599999999999</v>
       </c>
     </row>
@@ -3825,11 +3843,11 @@
         <v>31.367999999999999</v>
       </c>
       <c r="J69" s="6">
-        <f>G69*0.94-H69</f>
+        <f t="shared" si="4"/>
         <v>29.0154</v>
       </c>
       <c r="L69" s="6">
-        <f>J69-K69</f>
+        <f t="shared" si="5"/>
         <v>29.0154</v>
       </c>
     </row>
@@ -3862,11 +3880,11 @@
         <v>22.648</v>
       </c>
       <c r="J70" s="6">
-        <f>G70*0.94-H70</f>
+        <f t="shared" si="4"/>
         <v>20.949399999999997</v>
       </c>
       <c r="L70" s="6">
-        <f>J70-K70</f>
+        <f t="shared" si="5"/>
         <v>20.949399999999997</v>
       </c>
     </row>
@@ -3896,12 +3914,12 @@
         <v>11.704000000000001</v>
       </c>
       <c r="J71" s="6">
-        <f>G71*0.94-H71</f>
+        <f t="shared" si="4"/>
         <v>10.8262</v>
       </c>
       <c r="K71"/>
       <c r="L71" s="6">
-        <f>J71-K71</f>
+        <f t="shared" si="5"/>
         <v>10.8262</v>
       </c>
     </row>
@@ -3934,11 +3952,11 @@
         <v>7.6230000000000002</v>
       </c>
       <c r="J72" s="6">
-        <f>G72*0.94-H72</f>
+        <f t="shared" si="4"/>
         <v>7.1148000000000007</v>
       </c>
       <c r="L72" s="6">
-        <f>J72-K72</f>
+        <f t="shared" si="5"/>
         <v>7.1148000000000007</v>
       </c>
     </row>
@@ -3971,11 +3989,11 @@
         <v>41.41</v>
       </c>
       <c r="J73" s="6">
-        <f>G73*0.94-H73</f>
+        <f t="shared" si="4"/>
         <v>38.925399999999996</v>
       </c>
       <c r="L73" s="6">
-        <f>J73-K73</f>
+        <f t="shared" si="5"/>
         <v>38.925399999999996</v>
       </c>
     </row>
@@ -4008,11 +4026,11 @@
         <v>33.651000000000003</v>
       </c>
       <c r="J74" s="6">
-        <f>G74*0.94-H74</f>
+        <f t="shared" si="4"/>
         <v>31.407599999999999</v>
       </c>
       <c r="L74" s="6">
-        <f>J74-K74</f>
+        <f t="shared" si="5"/>
         <v>31.407599999999999</v>
       </c>
     </row>
@@ -4045,11 +4063,11 @@
         <v>23.04</v>
       </c>
       <c r="J75" s="6">
-        <f>G75*0.94-H75</f>
+        <f t="shared" si="4"/>
         <v>21.504000000000001</v>
       </c>
       <c r="L75" s="6">
-        <f>J75-K75</f>
+        <f t="shared" si="5"/>
         <v>21.504000000000001</v>
       </c>
     </row>
@@ -4082,11 +4100,11 @@
         <v>30.584</v>
       </c>
       <c r="J76" s="6">
-        <f>G76*0.94-H76</f>
+        <f t="shared" si="4"/>
         <v>28.290199999999992</v>
       </c>
       <c r="L76" s="6">
-        <f>J76-K76</f>
+        <f t="shared" si="5"/>
         <v>28.290199999999992</v>
       </c>
     </row>
@@ -4119,11 +4137,11 @@
         <v>32.095999999999997</v>
       </c>
       <c r="J77" s="6">
-        <f>G77*0.94-H77</f>
+        <f t="shared" si="4"/>
         <v>29.688799999999993</v>
       </c>
       <c r="L77" s="6">
-        <f>J77-K77</f>
+        <f t="shared" si="5"/>
         <v>29.688799999999993</v>
       </c>
     </row>
@@ -4156,12 +4174,12 @@
         <v>20.574000000000002</v>
       </c>
       <c r="J78" s="6">
-        <f>G78*0.94-H78</f>
+        <f t="shared" si="4"/>
         <v>19.202399999999997</v>
       </c>
       <c r="K78"/>
       <c r="L78" s="6">
-        <f>J78-K78</f>
+        <f t="shared" si="5"/>
         <v>19.202399999999997</v>
       </c>
     </row>
@@ -4194,11 +4212,11 @@
         <v>5.6340000000000003</v>
       </c>
       <c r="J79" s="6">
-        <f>G79*0.94-H79</f>
+        <f t="shared" si="4"/>
         <v>5.2583999999999991</v>
       </c>
       <c r="L79" s="6">
-        <f>J79-K79</f>
+        <f t="shared" si="5"/>
         <v>5.2583999999999991</v>
       </c>
     </row>
@@ -4231,11 +4249,11 @@
         <v>20.457000000000001</v>
       </c>
       <c r="J80" s="6">
-        <f>G80*0.94-H80</f>
+        <f t="shared" si="4"/>
         <v>19.0932</v>
       </c>
       <c r="L80" s="6">
-        <f>J80-K80</f>
+        <f t="shared" si="5"/>
         <v>19.0932</v>
       </c>
     </row>
@@ -4268,11 +4286,11 @@
         <v>28.539000000000001</v>
       </c>
       <c r="J81" s="6">
-        <f>G81*0.94-H81</f>
+        <f t="shared" si="4"/>
         <v>26.636399999999998</v>
       </c>
       <c r="L81" s="6">
-        <f>J81-K81</f>
+        <f t="shared" si="5"/>
         <v>26.636399999999998</v>
       </c>
     </row>
@@ -4305,11 +4323,11 @@
         <v>6.21</v>
       </c>
       <c r="J82" s="6">
-        <f>G82*0.94-H82</f>
+        <f t="shared" si="4"/>
         <v>5.7959999999999994</v>
       </c>
       <c r="L82" s="6">
-        <f>J82-K82</f>
+        <f t="shared" si="5"/>
         <v>5.7959999999999994</v>
       </c>
     </row>
@@ -4342,11 +4360,11 @@
         <v>43.45</v>
       </c>
       <c r="J83" s="6">
-        <f>G83*0.94-H83</f>
+        <f t="shared" si="4"/>
         <v>40.843000000000004</v>
       </c>
       <c r="L83" s="6">
-        <f>J83-K83</f>
+        <f t="shared" si="5"/>
         <v>40.843000000000004</v>
       </c>
     </row>
@@ -4379,11 +4397,11 @@
         <v>53.49</v>
       </c>
       <c r="J84" s="6">
-        <f>G84*0.94-H84</f>
+        <f t="shared" si="4"/>
         <v>50.2806</v>
       </c>
       <c r="L84" s="6">
-        <f>J84-K84</f>
+        <f t="shared" si="5"/>
         <v>50.2806</v>
       </c>
     </row>
@@ -4416,11 +4434,11 @@
         <v>38.82</v>
       </c>
       <c r="J85" s="6">
-        <f>G85*0.94-H85</f>
+        <f t="shared" si="4"/>
         <v>36.4908</v>
       </c>
       <c r="L85" s="6">
-        <f>J85-K85</f>
+        <f t="shared" si="5"/>
         <v>36.4908</v>
       </c>
     </row>
@@ -4453,11 +4471,11 @@
         <v>51.66</v>
       </c>
       <c r="J86" s="6">
-        <f>G86*0.94-H86</f>
+        <f t="shared" si="4"/>
         <v>48.560399999999994</v>
       </c>
       <c r="L86" s="6">
-        <f>J86-K86</f>
+        <f t="shared" si="5"/>
         <v>48.560399999999994</v>
       </c>
     </row>
@@ -4490,11 +4508,11 @@
         <v>28.1</v>
       </c>
       <c r="J87" s="6">
-        <f>G87*0.94-H87</f>
+        <f t="shared" si="4"/>
         <v>26.414000000000001</v>
       </c>
       <c r="L87" s="6">
-        <f>J87-K87</f>
+        <f t="shared" si="5"/>
         <v>26.414000000000001</v>
       </c>
     </row>
@@ -4527,11 +4545,11 @@
         <v>25.667999999999999</v>
       </c>
       <c r="J88" s="6">
-        <f>G88*0.94-H88</f>
+        <f t="shared" si="4"/>
         <v>23.956799999999998</v>
       </c>
       <c r="L88" s="6">
-        <f>J88-K88</f>
+        <f t="shared" si="5"/>
         <v>23.956799999999998</v>
       </c>
     </row>
@@ -4564,11 +4582,11 @@
         <v>11.93</v>
       </c>
       <c r="J89" s="6">
-        <f>G89*0.94-H89</f>
+        <f t="shared" si="4"/>
         <v>11.2142</v>
       </c>
       <c r="L89" s="6">
-        <f>J89-K89</f>
+        <f t="shared" si="5"/>
         <v>11.2142</v>
       </c>
     </row>
@@ -4601,11 +4619,11 @@
         <v>19.943999999999999</v>
       </c>
       <c r="J90" s="6">
-        <f>G90*0.94-H90</f>
+        <f t="shared" si="4"/>
         <v>18.614399999999996</v>
       </c>
       <c r="L90" s="6">
-        <f>J90-K90</f>
+        <f t="shared" si="5"/>
         <v>18.614399999999996</v>
       </c>
     </row>
@@ -4638,11 +4656,11 @@
         <v>25.44</v>
       </c>
       <c r="J91" s="6">
-        <f>G91*0.94-H91</f>
+        <f t="shared" si="4"/>
         <v>23.913599999999999</v>
       </c>
       <c r="L91" s="6">
-        <f>J91-K91</f>
+        <f t="shared" si="5"/>
         <v>23.913599999999999</v>
       </c>
     </row>
@@ -4675,11 +4693,11 @@
         <v>11.124000000000001</v>
       </c>
       <c r="J92" s="6">
-        <f>G92*0.94-H92</f>
+        <f t="shared" si="4"/>
         <v>10.382399999999999</v>
       </c>
       <c r="L92" s="6">
-        <f>J92-K92</f>
+        <f t="shared" si="5"/>
         <v>10.382399999999999</v>
       </c>
     </row>
@@ -4712,11 +4730,11 @@
         <v>13.581</v>
       </c>
       <c r="J93" s="6">
-        <f>G93*0.94-H93</f>
+        <f t="shared" si="4"/>
         <v>12.675599999999999</v>
       </c>
       <c r="L93" s="6">
-        <f>J93-K93</f>
+        <f t="shared" si="5"/>
         <v>12.675599999999999</v>
       </c>
     </row>
@@ -4749,11 +4767,11 @@
         <v>21.195</v>
       </c>
       <c r="J94" s="6">
-        <f>G94*0.94-H94</f>
+        <f t="shared" si="4"/>
         <v>19.782</v>
       </c>
       <c r="L94" s="6">
-        <f>J94-K94</f>
+        <f t="shared" si="5"/>
         <v>19.782</v>
       </c>
     </row>
@@ -4786,11 +4804,11 @@
         <v>35.945999999999998</v>
       </c>
       <c r="J95" s="6">
-        <f>G95*0.94-H95</f>
+        <f t="shared" si="4"/>
         <v>33.549599999999998</v>
       </c>
       <c r="L95" s="6">
-        <f>J95-K95</f>
+        <f t="shared" si="5"/>
         <v>33.549599999999998</v>
       </c>
     </row>
@@ -4823,11 +4841,11 @@
         <v>10.029999999999999</v>
       </c>
       <c r="J96" s="6">
-        <f>G96*0.94-H96</f>
+        <f t="shared" si="4"/>
         <v>9.4281999999999986</v>
       </c>
       <c r="L96" s="6">
-        <f>J96-K96</f>
+        <f t="shared" si="5"/>
         <v>9.4281999999999986</v>
       </c>
     </row>
@@ -4860,11 +4878,11 @@
         <v>14.696999999999999</v>
       </c>
       <c r="J97" s="6">
-        <f>G97*0.94-H97</f>
+        <f t="shared" si="4"/>
         <v>13.717199999999998</v>
       </c>
       <c r="L97" s="6">
-        <f>J97-K97</f>
+        <f t="shared" si="5"/>
         <v>13.717199999999998</v>
       </c>
     </row>
@@ -4897,11 +4915,11 @@
         <v>23.076000000000001</v>
       </c>
       <c r="J98" s="6">
-        <f>G98*0.94-H98</f>
+        <f t="shared" ref="J98:J129" si="6">G98*0.94-H98</f>
         <v>21.537599999999998</v>
       </c>
       <c r="L98" s="6">
-        <f>J98-K98</f>
+        <f t="shared" ref="L98:L129" si="7">J98-K98</f>
         <v>21.537599999999998</v>
       </c>
     </row>
@@ -4934,11 +4952,11 @@
         <v>8.9700000000000006</v>
       </c>
       <c r="J99" s="6">
-        <f>G99*0.94-H99</f>
+        <f t="shared" si="6"/>
         <v>8.4318000000000008</v>
       </c>
       <c r="L99" s="6">
-        <f>J99-K99</f>
+        <f t="shared" si="7"/>
         <v>8.4318000000000008</v>
       </c>
     </row>
@@ -4971,11 +4989,11 @@
         <v>16.794</v>
       </c>
       <c r="J100" s="6">
-        <f>G100*0.94-H100</f>
+        <f t="shared" si="6"/>
         <v>15.674399999999999</v>
       </c>
       <c r="L100" s="6">
-        <f>J100-K100</f>
+        <f t="shared" si="7"/>
         <v>15.674399999999999</v>
       </c>
     </row>
@@ -5008,12 +5026,12 @@
         <v>18.369</v>
       </c>
       <c r="J101" s="6">
-        <f>G101*0.94-H101</f>
+        <f t="shared" si="6"/>
         <v>17.144399999999997</v>
       </c>
       <c r="K101"/>
       <c r="L101" s="6">
-        <f>J101-K101</f>
+        <f t="shared" si="7"/>
         <v>17.144399999999997</v>
       </c>
     </row>
@@ -5046,11 +5064,11 @@
         <v>53.856000000000002</v>
       </c>
       <c r="J102" s="6">
-        <f>G102*0.94-H102</f>
+        <f t="shared" si="6"/>
         <v>50.265599999999999</v>
       </c>
       <c r="L102" s="6">
-        <f>J102-K102</f>
+        <f t="shared" si="7"/>
         <v>50.265599999999999</v>
       </c>
     </row>
@@ -5083,11 +5101,11 @@
         <v>21.338999999999999</v>
       </c>
       <c r="J103" s="6">
-        <f>G103*0.94-H103</f>
+        <f t="shared" si="6"/>
         <v>19.916399999999999</v>
       </c>
       <c r="L103" s="6">
-        <f>J103-K103</f>
+        <f t="shared" si="7"/>
         <v>19.916399999999999</v>
       </c>
     </row>
@@ -5120,11 +5138,11 @@
         <v>26.361000000000001</v>
       </c>
       <c r="J104" s="6">
-        <f>G104*0.94-H104</f>
+        <f t="shared" si="6"/>
         <v>24.6036</v>
       </c>
       <c r="L104" s="6">
-        <f>J104-K104</f>
+        <f t="shared" si="7"/>
         <v>24.6036</v>
       </c>
     </row>
@@ -5157,11 +5175,11 @@
         <v>30.824999999999999</v>
       </c>
       <c r="J105" s="6">
-        <f>G105*0.94-H105</f>
+        <f t="shared" si="6"/>
         <v>28.77</v>
       </c>
       <c r="L105" s="6">
-        <f>J105-K105</f>
+        <f t="shared" si="7"/>
         <v>28.77</v>
       </c>
     </row>
@@ -5194,11 +5212,11 @@
         <v>46.11</v>
       </c>
       <c r="J106" s="6">
-        <f>G106*0.94-H106</f>
+        <f t="shared" si="6"/>
         <v>43.343399999999995</v>
       </c>
       <c r="L106" s="6">
-        <f>J106-K106</f>
+        <f t="shared" si="7"/>
         <v>43.343399999999995</v>
       </c>
     </row>
@@ -5231,11 +5249,11 @@
         <v>17.901</v>
       </c>
       <c r="J107" s="6">
-        <f>G107*0.94-H107</f>
+        <f t="shared" si="6"/>
         <v>16.707599999999999</v>
       </c>
       <c r="L107" s="6">
-        <f>J107-K107</f>
+        <f t="shared" si="7"/>
         <v>16.707599999999999</v>
       </c>
     </row>
@@ -5268,11 +5286,11 @@
         <v>5.1029999999999998</v>
       </c>
       <c r="J108" s="6">
-        <f>G108*0.94-H108</f>
+        <f t="shared" si="6"/>
         <v>4.7627999999999995</v>
       </c>
       <c r="L108" s="6">
-        <f>J108-K108</f>
+        <f t="shared" si="7"/>
         <v>4.7627999999999995</v>
       </c>
     </row>
@@ -5305,11 +5323,11 @@
         <v>11.664</v>
       </c>
       <c r="J109" s="6">
-        <f>G109*0.94-H109</f>
+        <f t="shared" si="6"/>
         <v>10.8864</v>
       </c>
       <c r="L109" s="6">
-        <f>J109-K109</f>
+        <f t="shared" si="7"/>
         <v>10.8864</v>
       </c>
     </row>
@@ -5342,11 +5360,11 @@
         <v>21.140999999999998</v>
       </c>
       <c r="J110" s="6">
-        <f>G110*0.94-H110</f>
+        <f t="shared" si="6"/>
         <v>19.731599999999997</v>
       </c>
       <c r="L110" s="6">
-        <f>J110-K110</f>
+        <f t="shared" si="7"/>
         <v>19.731599999999997</v>
       </c>
     </row>
@@ -5379,11 +5397,11 @@
         <v>22.841999999999999</v>
       </c>
       <c r="J111" s="6">
-        <f>G111*0.94-H111</f>
+        <f t="shared" si="6"/>
         <v>21.319199999999999</v>
       </c>
       <c r="L111" s="6">
-        <f>J111-K111</f>
+        <f t="shared" si="7"/>
         <v>21.319199999999999</v>
       </c>
     </row>
@@ -5416,11 +5434,11 @@
         <v>25.766999999999999</v>
       </c>
       <c r="J112" s="6">
-        <f>G112*0.94-H112</f>
+        <f t="shared" si="6"/>
         <v>24.049199999999999</v>
       </c>
       <c r="L112" s="6">
-        <f>J112-K112</f>
+        <f t="shared" si="7"/>
         <v>24.049199999999999</v>
       </c>
     </row>
@@ -5453,11 +5471,11 @@
         <v>35.451000000000001</v>
       </c>
       <c r="J113" s="6">
-        <f>G113*0.94-H113</f>
+        <f t="shared" si="6"/>
         <v>33.087600000000002</v>
       </c>
       <c r="L113" s="6">
-        <f>J113-K113</f>
+        <f t="shared" si="7"/>
         <v>33.087600000000002</v>
       </c>
     </row>
@@ -5490,11 +5508,11 @@
         <v>21.645</v>
       </c>
       <c r="J114" s="6">
-        <f>G114*0.94-H114</f>
+        <f t="shared" si="6"/>
         <v>20.201999999999998</v>
       </c>
       <c r="L114" s="6">
-        <f>J114-K114</f>
+        <f t="shared" si="7"/>
         <v>20.201999999999998</v>
       </c>
     </row>
@@ -5527,11 +5545,11 @@
         <v>34.938000000000002</v>
       </c>
       <c r="J115" s="6">
-        <f>G115*0.94-H115</f>
+        <f t="shared" si="6"/>
         <v>32.608800000000002</v>
       </c>
       <c r="L115" s="6">
-        <f>J115-K115</f>
+        <f t="shared" si="7"/>
         <v>32.608800000000002</v>
       </c>
     </row>
@@ -5564,12 +5582,12 @@
         <v>9.5850000000000009</v>
       </c>
       <c r="J116" s="6">
-        <f>G116*0.94-H116</f>
+        <f t="shared" si="6"/>
         <v>8.9459999999999997</v>
       </c>
       <c r="K116"/>
       <c r="L116" s="6">
-        <f>J116-K116</f>
+        <f t="shared" si="7"/>
         <v>8.9459999999999997</v>
       </c>
     </row>
@@ -5602,12 +5620,12 @@
         <v>8.7390000000000008</v>
       </c>
       <c r="J117" s="6">
-        <f>G117*0.94-H117</f>
+        <f t="shared" si="6"/>
         <v>8.1563999999999997</v>
       </c>
       <c r="K117"/>
       <c r="L117" s="6">
-        <f>J117-K117</f>
+        <f t="shared" si="7"/>
         <v>8.1563999999999997</v>
       </c>
     </row>
@@ -5640,12 +5658,12 @@
         <v>14.67</v>
       </c>
       <c r="J118" s="6">
-        <f>G118*0.94-H118</f>
+        <f t="shared" si="6"/>
         <v>13.692</v>
       </c>
       <c r="K118"/>
       <c r="L118" s="6">
-        <f>J118-K118</f>
+        <f t="shared" si="7"/>
         <v>13.692</v>
       </c>
     </row>
@@ -5678,12 +5696,12 @@
         <v>16.632000000000001</v>
       </c>
       <c r="J119" s="6">
-        <f>G119*0.94-H119</f>
+        <f t="shared" si="6"/>
         <v>15.523199999999997</v>
       </c>
       <c r="K119"/>
       <c r="L119" s="6">
-        <f>J119-K119</f>
+        <f t="shared" si="7"/>
         <v>15.523199999999997</v>
       </c>
     </row>
@@ -5716,11 +5734,11 @@
         <v>19.071000000000002</v>
       </c>
       <c r="J120" s="6">
-        <f>G120*0.94-H120</f>
+        <f t="shared" si="6"/>
         <v>17.799600000000002</v>
       </c>
       <c r="L120" s="6">
-        <f>J120-K120</f>
+        <f t="shared" si="7"/>
         <v>17.799600000000002</v>
       </c>
     </row>
@@ -5753,11 +5771,11 @@
         <v>38.15</v>
       </c>
       <c r="J121" s="6">
-        <f>G121*0.94-H121</f>
+        <f t="shared" si="6"/>
         <v>35.860999999999997</v>
       </c>
       <c r="L121" s="6">
-        <f>J121-K121</f>
+        <f t="shared" si="7"/>
         <v>35.860999999999997</v>
       </c>
     </row>
@@ -5790,11 +5808,11 @@
         <v>6.57</v>
       </c>
       <c r="J122" s="6">
-        <f>G122*0.94-H122</f>
+        <f t="shared" si="6"/>
         <v>6.1757999999999997</v>
       </c>
       <c r="L122" s="6">
-        <f>J122-K122</f>
+        <f t="shared" si="7"/>
         <v>6.1757999999999997</v>
       </c>
     </row>
@@ -5827,11 +5845,11 @@
         <v>33.633000000000003</v>
       </c>
       <c r="J123" s="6">
-        <f>G123*0.94-H123</f>
+        <f t="shared" si="6"/>
         <v>31.390799999999992</v>
       </c>
       <c r="L123" s="6">
-        <f>J123-K123</f>
+        <f t="shared" si="7"/>
         <v>31.390799999999992</v>
       </c>
     </row>
@@ -5864,11 +5882,11 @@
         <v>9.7289999999999992</v>
       </c>
       <c r="J124" s="6">
-        <f>G124*0.94-H124</f>
+        <f t="shared" si="6"/>
         <v>9.0804000000000009</v>
       </c>
       <c r="L124" s="6">
-        <f>J124-K124</f>
+        <f t="shared" si="7"/>
         <v>9.0804000000000009</v>
       </c>
     </row>
@@ -5901,11 +5919,11 @@
         <v>13.18</v>
       </c>
       <c r="J125" s="6">
-        <f>G125*0.94-H125</f>
+        <f t="shared" si="6"/>
         <v>12.389199999999999</v>
       </c>
       <c r="L125" s="6">
-        <f>J125-K125</f>
+        <f t="shared" si="7"/>
         <v>12.389199999999999</v>
       </c>
     </row>
@@ -5938,11 +5956,11 @@
         <v>29.2</v>
       </c>
       <c r="J126" s="6">
-        <f>G126*0.94-H126</f>
+        <f t="shared" si="6"/>
         <v>27.447999999999997</v>
       </c>
       <c r="L126" s="6">
-        <f>J126-K126</f>
+        <f t="shared" si="7"/>
         <v>27.447999999999997</v>
       </c>
     </row>
@@ -5975,11 +5993,11 @@
         <v>29.655000000000001</v>
       </c>
       <c r="J127" s="6">
-        <f>G127*0.94-H127</f>
+        <f t="shared" si="6"/>
         <v>27.678000000000004</v>
       </c>
       <c r="L127" s="6">
-        <f>J127-K127</f>
+        <f t="shared" si="7"/>
         <v>27.678000000000004</v>
       </c>
     </row>
@@ -6012,11 +6030,11 @@
         <v>33.444000000000003</v>
       </c>
       <c r="J128" s="6">
-        <f>G128*0.94-H128</f>
+        <f t="shared" si="6"/>
         <v>31.214399999999991</v>
       </c>
       <c r="L128" s="6">
-        <f>J128-K128</f>
+        <f t="shared" si="7"/>
         <v>31.214399999999991</v>
       </c>
     </row>
@@ -6049,11 +6067,11 @@
         <v>33.642000000000003</v>
       </c>
       <c r="J129" s="6">
-        <f>G129*0.94-H129</f>
+        <f t="shared" si="6"/>
         <v>31.3992</v>
       </c>
       <c r="L129" s="6">
-        <f>J129-K129</f>
+        <f t="shared" si="7"/>
         <v>31.3992</v>
       </c>
     </row>
@@ -6086,11 +6104,11 @@
         <v>33.93</v>
       </c>
       <c r="J130" s="6">
-        <f>G130*0.94-H130</f>
+        <f t="shared" ref="J130:J161" si="8">G130*0.94-H130</f>
         <v>31.668000000000003</v>
       </c>
       <c r="L130" s="6">
-        <f>J130-K130</f>
+        <f t="shared" ref="L130:L161" si="9">J130-K130</f>
         <v>31.668000000000003</v>
       </c>
     </row>
@@ -6123,12 +6141,12 @@
         <v>8.7479999999999993</v>
       </c>
       <c r="J131" s="6">
-        <f>G131*0.94-H131</f>
+        <f t="shared" si="8"/>
         <v>8.1648000000000014</v>
       </c>
       <c r="K131"/>
       <c r="L131" s="6">
-        <f>J131-K131</f>
+        <f t="shared" si="9"/>
         <v>8.1648000000000014</v>
       </c>
     </row>
@@ -6161,11 +6179,11 @@
         <v>13.99</v>
       </c>
       <c r="J132" s="6">
-        <f>G132*0.94-H132</f>
+        <f t="shared" si="8"/>
         <v>13.150599999999999</v>
       </c>
       <c r="L132" s="6">
-        <f>J132-K132</f>
+        <f t="shared" si="9"/>
         <v>13.150599999999999</v>
       </c>
     </row>
@@ -6198,11 +6216,11 @@
         <v>51.04</v>
       </c>
       <c r="J133" s="6">
-        <f>G133*0.94-H133</f>
+        <f t="shared" si="8"/>
         <v>47.977599999999995</v>
       </c>
       <c r="L133" s="6">
-        <f>J133-K133</f>
+        <f t="shared" si="9"/>
         <v>47.977599999999995</v>
       </c>
     </row>
@@ -6235,11 +6253,11 @@
         <v>8.91</v>
       </c>
       <c r="J134" s="6">
-        <f>G134*0.94-H134</f>
+        <f t="shared" si="8"/>
         <v>8.3753999999999991</v>
       </c>
       <c r="L134" s="6">
-        <f>J134-K134</f>
+        <f t="shared" si="9"/>
         <v>8.3753999999999991</v>
       </c>
     </row>
@@ -6272,11 +6290,11 @@
         <v>9.5850000000000009</v>
       </c>
       <c r="J135" s="6">
-        <f>G135*0.94-H135</f>
+        <f t="shared" si="8"/>
         <v>8.9459999999999997</v>
       </c>
       <c r="L135" s="6">
-        <f>J135-K135</f>
+        <f t="shared" si="9"/>
         <v>8.9459999999999997</v>
       </c>
     </row>
@@ -6309,11 +6327,11 @@
         <v>22.113</v>
       </c>
       <c r="J136" s="6">
-        <f>G136*0.94-H136</f>
+        <f t="shared" si="8"/>
         <v>20.6388</v>
       </c>
       <c r="L136" s="6">
-        <f>J136-K136</f>
+        <f t="shared" si="9"/>
         <v>20.6388</v>
       </c>
     </row>
@@ -6346,11 +6364,11 @@
         <v>17.433</v>
       </c>
       <c r="J137" s="6">
-        <f>G137*0.94-H137</f>
+        <f t="shared" si="8"/>
         <v>16.270799999999998</v>
       </c>
       <c r="L137" s="6">
-        <f>J137-K137</f>
+        <f t="shared" si="9"/>
         <v>16.270799999999998</v>
       </c>
     </row>
@@ -6383,11 +6401,11 @@
         <v>27.972000000000001</v>
       </c>
       <c r="J138" s="6">
-        <f>G138*0.94-H138</f>
+        <f t="shared" si="8"/>
         <v>26.107199999999995</v>
       </c>
       <c r="L138" s="6">
-        <f>J138-K138</f>
+        <f t="shared" si="9"/>
         <v>26.107199999999995</v>
       </c>
     </row>
@@ -6420,11 +6438,11 @@
         <v>6.7590000000000003</v>
       </c>
       <c r="J139" s="6">
-        <f>G139*0.94-H139</f>
+        <f t="shared" si="8"/>
         <v>6.3083999999999989</v>
       </c>
       <c r="L139" s="6">
-        <f>J139-K139</f>
+        <f t="shared" si="9"/>
         <v>6.3083999999999989</v>
       </c>
     </row>
@@ -6457,11 +6475,11 @@
         <v>39.807000000000002</v>
       </c>
       <c r="J140" s="6">
-        <f>G140*0.94-H140</f>
+        <f t="shared" si="8"/>
         <v>37.153199999999991</v>
       </c>
       <c r="L140" s="6">
-        <f>J140-K140</f>
+        <f t="shared" si="9"/>
         <v>37.153199999999991</v>
       </c>
     </row>
@@ -6494,11 +6512,11 @@
         <v>48.942</v>
       </c>
       <c r="J141" s="6">
-        <f>G141*0.94-H141</f>
+        <f t="shared" si="8"/>
         <v>45.679199999999994</v>
       </c>
       <c r="L141" s="6">
-        <f>J141-K141</f>
+        <f t="shared" si="9"/>
         <v>45.679199999999994</v>
       </c>
     </row>
@@ -6531,11 +6549,11 @@
         <v>37.917000000000002</v>
       </c>
       <c r="J142" s="6">
-        <f>G142*0.94-H142</f>
+        <f t="shared" si="8"/>
         <v>35.389200000000002</v>
       </c>
       <c r="L142" s="6">
-        <f>J142-K142</f>
+        <f t="shared" si="9"/>
         <v>35.389200000000002</v>
       </c>
     </row>
@@ -6568,11 +6586,11 @@
         <v>29.870999999999999</v>
       </c>
       <c r="J143" s="6">
-        <f>G143*0.94-H143</f>
+        <f t="shared" si="8"/>
         <v>27.879599999999996</v>
       </c>
       <c r="L143" s="6">
-        <f>J143-K143</f>
+        <f t="shared" si="9"/>
         <v>27.879599999999996</v>
       </c>
     </row>
@@ -6605,11 +6623,11 @@
         <v>50.030999999999999</v>
       </c>
       <c r="J144" s="6">
-        <f>G144*0.94-H144</f>
+        <f t="shared" si="8"/>
         <v>46.695600000000006</v>
       </c>
       <c r="L144" s="6">
-        <f>J144-K144</f>
+        <f t="shared" si="9"/>
         <v>46.695600000000006</v>
       </c>
     </row>
@@ -6642,11 +6660,11 @@
         <v>40.590000000000003</v>
       </c>
       <c r="J145" s="6">
-        <f>G145*0.94-H145</f>
+        <f t="shared" si="8"/>
         <v>37.884</v>
       </c>
       <c r="L145" s="6">
-        <f>J145-K145</f>
+        <f t="shared" si="9"/>
         <v>37.884</v>
       </c>
     </row>
@@ -6679,11 +6697,11 @@
         <v>4.3499999999999996</v>
       </c>
       <c r="J146" s="6">
-        <f>G146*0.94-H146</f>
+        <f t="shared" si="8"/>
         <v>4.0889999999999995</v>
       </c>
       <c r="L146" s="6">
-        <f>J146-K146</f>
+        <f t="shared" si="9"/>
         <v>4.0889999999999995</v>
       </c>
     </row>
@@ -6716,11 +6734,11 @@
         <v>19.899999999999999</v>
       </c>
       <c r="J147" s="6">
-        <f>G147*0.94-H147</f>
+        <f t="shared" si="8"/>
         <v>18.705999999999996</v>
       </c>
       <c r="L147" s="6">
-        <f>J147-K147</f>
+        <f t="shared" si="9"/>
         <v>18.705999999999996</v>
       </c>
     </row>
@@ -6753,11 +6771,11 @@
         <v>48.69</v>
       </c>
       <c r="J148" s="6">
-        <f>G148*0.94-H148</f>
+        <f t="shared" si="8"/>
         <v>45.444000000000003</v>
       </c>
       <c r="L148" s="6">
-        <f>J148-K148</f>
+        <f t="shared" si="9"/>
         <v>45.444000000000003</v>
       </c>
     </row>
@@ -6790,11 +6808,11 @@
         <v>51.19</v>
       </c>
       <c r="J149" s="6">
-        <f>G149*0.94-H149</f>
+        <f t="shared" si="8"/>
         <v>48.118599999999994</v>
       </c>
       <c r="L149" s="6">
-        <f>J149-K149</f>
+        <f t="shared" si="9"/>
         <v>48.118599999999994</v>
       </c>
     </row>
@@ -6827,11 +6845,11 @@
         <v>31.446000000000002</v>
       </c>
       <c r="J150" s="6">
-        <f>G150*0.94-H150</f>
+        <f t="shared" si="8"/>
         <v>29.349599999999995</v>
       </c>
       <c r="L150" s="6">
-        <f>J150-K150</f>
+        <f t="shared" si="9"/>
         <v>29.349599999999995</v>
       </c>
     </row>
@@ -6864,12 +6882,12 @@
         <v>36</v>
       </c>
       <c r="J151" s="6">
-        <f>G151*0.94-H151</f>
+        <f t="shared" si="8"/>
         <v>33.599999999999994</v>
       </c>
       <c r="K151"/>
       <c r="L151" s="6">
-        <f>J151-K151</f>
+        <f t="shared" si="9"/>
         <v>33.599999999999994</v>
       </c>
     </row>
@@ -6902,12 +6920,12 @@
         <v>29.07</v>
       </c>
       <c r="J152" s="6">
-        <f>G152*0.94-H152</f>
+        <f t="shared" si="8"/>
         <v>27.325799999999997</v>
       </c>
       <c r="K152"/>
       <c r="L152" s="6">
-        <f>J152-K152</f>
+        <f t="shared" si="9"/>
         <v>27.325799999999997</v>
       </c>
     </row>
@@ -6940,12 +6958,12 @@
         <v>23.472000000000001</v>
       </c>
       <c r="J153" s="6">
-        <f>G153*0.94-H153</f>
+        <f t="shared" si="8"/>
         <v>21.907199999999996</v>
       </c>
       <c r="K153"/>
       <c r="L153" s="6">
-        <f>J153-K153</f>
+        <f t="shared" si="9"/>
         <v>21.907199999999996</v>
       </c>
     </row>
@@ -6978,12 +6996,12 @@
         <v>28.053000000000001</v>
       </c>
       <c r="J154" s="6">
-        <f>G154*0.94-H154</f>
+        <f t="shared" si="8"/>
         <v>26.1828</v>
       </c>
       <c r="K154"/>
       <c r="L154" s="6">
-        <f>J154-K154</f>
+        <f t="shared" si="9"/>
         <v>26.1828</v>
       </c>
     </row>
@@ -7016,12 +7034,12 @@
         <v>24.228000000000002</v>
       </c>
       <c r="J155" s="6">
-        <f>G155*0.94-H155</f>
+        <f t="shared" si="8"/>
         <v>22.6128</v>
       </c>
       <c r="K155"/>
       <c r="L155" s="6">
-        <f>J155-K155</f>
+        <f t="shared" si="9"/>
         <v>22.6128</v>
       </c>
     </row>
@@ -7054,12 +7072,12 @@
         <v>24.88</v>
       </c>
       <c r="J156" s="6">
-        <f>G156*0.94-H156</f>
+        <f t="shared" si="8"/>
         <v>23.387199999999996</v>
       </c>
       <c r="K156"/>
       <c r="L156" s="6">
-        <f>J156-K156</f>
+        <f t="shared" si="9"/>
         <v>23.387199999999996</v>
       </c>
     </row>
@@ -7092,12 +7110,12 @@
         <v>40.122</v>
       </c>
       <c r="J157" s="6">
-        <f>G157*0.94-H157</f>
+        <f t="shared" si="8"/>
         <v>37.447199999999995</v>
       </c>
       <c r="K157"/>
       <c r="L157" s="6">
-        <f>J157-K157</f>
+        <f t="shared" si="9"/>
         <v>37.447199999999995</v>
       </c>
     </row>
@@ -7130,12 +7148,12 @@
         <v>4.0229999999999997</v>
       </c>
       <c r="J158" s="6">
-        <f>G158*0.94-H158</f>
+        <f t="shared" si="8"/>
         <v>3.7547999999999995</v>
       </c>
       <c r="K158"/>
       <c r="L158" s="6">
-        <f>J158-K158</f>
+        <f t="shared" si="9"/>
         <v>3.7547999999999995</v>
       </c>
     </row>
@@ -7168,12 +7186,12 @@
         <v>43.082999999999998</v>
       </c>
       <c r="J159" s="6">
-        <f>G159*0.94-H159</f>
+        <f t="shared" si="8"/>
         <v>40.210799999999999</v>
       </c>
       <c r="K159"/>
       <c r="L159" s="6">
-        <f>J159-K159</f>
+        <f t="shared" si="9"/>
         <v>40.210799999999999</v>
       </c>
     </row>
@@ -7206,12 +7224,12 @@
         <v>22.652999999999999</v>
       </c>
       <c r="J160" s="6">
-        <f>G160*0.94-H160</f>
+        <f t="shared" si="8"/>
         <v>21.142800000000001</v>
       </c>
       <c r="K160"/>
       <c r="L160" s="6">
-        <f>J160-K160</f>
+        <f t="shared" si="9"/>
         <v>21.142800000000001</v>
       </c>
     </row>
@@ -7244,12 +7262,12 @@
         <v>95.2</v>
       </c>
       <c r="J161" s="6">
-        <f>G161*0.94-H161</f>
+        <f t="shared" si="8"/>
         <v>89.488</v>
       </c>
       <c r="K161"/>
       <c r="L161" s="6">
-        <f>J161-K161</f>
+        <f t="shared" si="9"/>
         <v>89.488</v>
       </c>
     </row>
@@ -7282,12 +7300,12 @@
         <v>15.48</v>
       </c>
       <c r="J162" s="6">
-        <f>G162*0.94-H162</f>
+        <f t="shared" ref="J162:J174" si="10">G162*0.94-H162</f>
         <v>14.447999999999999</v>
       </c>
       <c r="K162"/>
       <c r="L162" s="6">
-        <f>J162-K162</f>
+        <f t="shared" ref="L162:L174" si="11">J162-K162</f>
         <v>14.447999999999999</v>
       </c>
     </row>
@@ -7320,11 +7338,11 @@
         <v>40.968000000000004</v>
       </c>
       <c r="J163" s="6">
-        <f>G163*0.94-H163</f>
+        <f t="shared" si="10"/>
         <v>38.236800000000002</v>
       </c>
       <c r="L163" s="6">
-        <f>J163-K163</f>
+        <f t="shared" si="11"/>
         <v>38.236800000000002</v>
       </c>
     </row>
@@ -7357,11 +7375,11 @@
         <v>29.405999999999999</v>
       </c>
       <c r="J164" s="6">
-        <f>G164*0.94-H164</f>
+        <f t="shared" si="10"/>
         <v>27.445620000000002</v>
       </c>
       <c r="L164" s="6">
-        <f>J164-K164</f>
+        <f t="shared" si="11"/>
         <v>27.445620000000002</v>
       </c>
     </row>
@@ -7394,11 +7412,11 @@
         <v>6.4980000000000002</v>
       </c>
       <c r="J165" s="6">
-        <f>G165*0.94-H165</f>
+        <f t="shared" si="10"/>
         <v>6.0648</v>
       </c>
       <c r="L165" s="6">
-        <f>J165-K165</f>
+        <f t="shared" si="11"/>
         <v>6.0648</v>
       </c>
     </row>
@@ -7431,11 +7449,11 @@
         <v>49.805999999999997</v>
       </c>
       <c r="J166" s="6">
-        <f>G166*0.94-H166</f>
+        <f t="shared" si="10"/>
         <v>46.485599999999998</v>
       </c>
       <c r="L166" s="6">
-        <f>J166-K166</f>
+        <f t="shared" si="11"/>
         <v>46.485599999999998</v>
       </c>
     </row>
@@ -7468,11 +7486,11 @@
         <v>37.368000000000002</v>
       </c>
       <c r="J167" s="6">
-        <f>G167*0.94-H167</f>
+        <f t="shared" si="10"/>
         <v>34.876800000000003</v>
       </c>
       <c r="L167" s="6">
-        <f>J167-K167</f>
+        <f t="shared" si="11"/>
         <v>34.876800000000003</v>
       </c>
     </row>
@@ -7505,11 +7523,11 @@
         <v>31.86</v>
       </c>
       <c r="J168" s="6">
-        <f>G168*0.94-H168</f>
+        <f t="shared" si="10"/>
         <v>29.735999999999997</v>
       </c>
       <c r="L168" s="6">
-        <f>J168-K168</f>
+        <f t="shared" si="11"/>
         <v>29.735999999999997</v>
       </c>
     </row>
@@ -7542,11 +7560,11 @@
         <v>42.273000000000003</v>
       </c>
       <c r="J169" s="6">
-        <f>G169*0.94-H169</f>
+        <f t="shared" si="10"/>
         <v>39.454799999999992</v>
       </c>
       <c r="L169" s="6">
-        <f>J169-K169</f>
+        <f t="shared" si="11"/>
         <v>39.454799999999992</v>
       </c>
     </row>
@@ -7579,11 +7597,11 @@
         <v>16.326000000000001</v>
       </c>
       <c r="J170" s="6">
-        <f>G170*0.94-H170</f>
+        <f t="shared" si="10"/>
         <v>15.2376</v>
       </c>
       <c r="L170" s="6">
-        <f>J170-K170</f>
+        <f t="shared" si="11"/>
         <v>15.2376</v>
       </c>
     </row>
@@ -7616,12 +7634,12 @@
         <v>37.65</v>
       </c>
       <c r="J171" s="6">
-        <f>G171*0.94-H171</f>
+        <f t="shared" si="10"/>
         <v>35.390999999999998</v>
       </c>
       <c r="K171"/>
       <c r="L171" s="6">
-        <f>J171-K171</f>
+        <f t="shared" si="11"/>
         <v>35.390999999999998</v>
       </c>
     </row>
@@ -7654,12 +7672,12 @@
         <v>3.4079999999999999</v>
       </c>
       <c r="J172" s="6">
-        <f>G172*0.94-H172</f>
+        <f t="shared" si="10"/>
         <v>3.1523999999999996</v>
       </c>
       <c r="K172"/>
       <c r="L172" s="6">
-        <f>J172-K172</f>
+        <f t="shared" si="11"/>
         <v>3.1523999999999996</v>
       </c>
     </row>
@@ -7692,12 +7710,12 @@
         <v>6.4240000000000004</v>
       </c>
       <c r="J173" s="6">
-        <f>G173*0.94-H173</f>
+        <f t="shared" si="10"/>
         <v>5.9421999999999988</v>
       </c>
       <c r="K173"/>
       <c r="L173" s="6">
-        <f>J173-K173</f>
+        <f t="shared" si="11"/>
         <v>5.9421999999999988</v>
       </c>
     </row>
@@ -7730,13 +7748,241 @@
         <v>40.661999999999999</v>
       </c>
       <c r="J174" s="6">
-        <f>G174*0.94-H174</f>
+        <f t="shared" si="10"/>
         <v>37.9512</v>
       </c>
       <c r="K174"/>
       <c r="L174" s="6">
-        <f>J174-K174</f>
+        <f t="shared" si="11"/>
         <v>37.9512</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
+        <v>1</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D175" s="2">
+        <v>803582957</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F175" s="3">
+        <v>46208</v>
+      </c>
+      <c r="G175" s="2">
+        <v>23.16</v>
+      </c>
+      <c r="H175" s="2">
+        <v>2.3159999999999998</v>
+      </c>
+      <c r="I175" s="2">
+        <v>20.844000000000001</v>
+      </c>
+      <c r="J175" s="6">
+        <f t="shared" ref="J175:J179" si="12">G175*0.94-H175</f>
+        <v>19.4544</v>
+      </c>
+      <c r="K175"/>
+      <c r="L175" s="6">
+        <f t="shared" ref="L175:L179" si="13">J175-K175</f>
+        <v>19.4544</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A176" s="2">
+        <v>2</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D176" s="2">
+        <v>803589459</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="3">
+        <v>46223</v>
+      </c>
+      <c r="G176" s="2">
+        <v>43.09</v>
+      </c>
+      <c r="H176" s="2">
+        <v>4.3090000000000002</v>
+      </c>
+      <c r="I176" s="2">
+        <v>38.780999999999999</v>
+      </c>
+      <c r="J176" s="6">
+        <f t="shared" si="12"/>
+        <v>36.195600000000006</v>
+      </c>
+      <c r="K176"/>
+      <c r="L176" s="6">
+        <f t="shared" si="13"/>
+        <v>36.195600000000006</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
+        <v>3</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D177" s="2">
+        <v>803590151</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177" s="3">
+        <v>46226</v>
+      </c>
+      <c r="G177" s="2">
+        <v>69.44</v>
+      </c>
+      <c r="H177" s="2">
+        <v>13.888</v>
+      </c>
+      <c r="I177" s="2">
+        <v>55.552</v>
+      </c>
+      <c r="J177" s="6">
+        <f t="shared" si="12"/>
+        <v>51.38559999999999</v>
+      </c>
+      <c r="K177"/>
+      <c r="L177" s="6">
+        <f t="shared" si="13"/>
+        <v>51.38559999999999</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>4</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D178" s="2">
+        <v>803590494</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F178" s="3">
+        <v>46226</v>
+      </c>
+      <c r="G178" s="2">
+        <v>34.840000000000003</v>
+      </c>
+      <c r="H178" s="2">
+        <v>0</v>
+      </c>
+      <c r="I178" s="2">
+        <v>34.840000000000003</v>
+      </c>
+      <c r="J178" s="6">
+        <f t="shared" si="12"/>
+        <v>32.749600000000001</v>
+      </c>
+      <c r="K178"/>
+      <c r="L178" s="6">
+        <f t="shared" si="13"/>
+        <v>32.749600000000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <v>5</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D179" s="2">
+        <v>803592452</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F179" s="3">
+        <v>46233</v>
+      </c>
+      <c r="G179" s="2">
+        <v>32.56</v>
+      </c>
+      <c r="H179" s="2">
+        <v>3.2559999999999998</v>
+      </c>
+      <c r="I179" s="2">
+        <v>29.303999999999998</v>
+      </c>
+      <c r="J179" s="6">
+        <f t="shared" si="12"/>
+        <v>27.3504</v>
+      </c>
+      <c r="K179"/>
+      <c r="L179" s="6">
+        <f t="shared" si="13"/>
+        <v>27.3504</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
+        <v>1</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D180" s="2">
+        <v>803592418</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F180" s="3">
+        <v>46232</v>
+      </c>
+      <c r="G180" s="2">
+        <v>15.64</v>
+      </c>
+      <c r="H180" s="2">
+        <v>1.5640000000000001</v>
+      </c>
+      <c r="I180" s="2">
+        <v>14.076000000000001</v>
+      </c>
+      <c r="J180" s="6">
+        <f>G180*0.94-H180</f>
+        <v>13.137599999999999</v>
+      </c>
+      <c r="K180"/>
+      <c r="L180" s="6">
+        <f>J180-K180</f>
+        <v>13.137599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/ميدسيرفس.xlsx
+++ b/ميدسيرفس.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E47913-00B2-4B78-BD59-9835E74C7CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77164BA9-E866-4FC6-863F-75B6E1AD4A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D788D8F7-2544-4C2F-9B89-70931910278C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="206">
   <si>
     <t>الرقم</t>
   </si>
@@ -651,6 +651,9 @@
   </si>
   <si>
     <t>ندا الحسنات</t>
+  </si>
+  <si>
+    <t>تاريخ الدفعة</t>
   </si>
 </sst>
 </file>
@@ -660,7 +663,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -685,6 +688,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -700,7 +708,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -708,11 +716,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -720,16 +741,187 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="27">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -802,7 +994,24 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -933,28 +1142,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}" name="Table1" displayName="Table1" ref="A1:L180" totalsRowShown="0" headerRowDxfId="11">
-  <autoFilter ref="A1:L180" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L174">
-    <sortCondition ref="F1:F174"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}" name="Table1" displayName="Table1" ref="A1:M181" totalsRowCount="1" headerRowDxfId="26">
+  <autoFilter ref="A1:M180" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L180">
+    <sortCondition ref="F1:F180"/>
   </sortState>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{60C6F871-C16F-4E0C-BCFA-8355ABD999C9}" name="الرقم" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{16663A49-EAEA-4D0C-AEE4-F16F12092E0B}" name="رقم الموظف /رقم البطاقة" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{E695BC9D-90B5-4017-835E-DE39F27EC4B5}" name="اسم المريض" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{4FA0F61B-0974-4290-8AF9-64F3425CF95F}" name="رقم النموذج" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{FA7C7B11-59CD-43FE-8614-AE77C814F7B1}" name="نوع المستفيد" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{A5C7FB1D-369A-430A-90FD-DECEB437BB07}" name="تاريخ البيع" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{A0C6C549-4E6F-40C8-8B90-0D7D85B722AF}" name="قيمة الفاتورة" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{FE5B0B26-736F-4D13-A599-E33B398493F1}" name="قيمة المشاركة" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{BC1FF825-92ED-4149-A1D2-B9B13F698346}" name="صافي القيمة" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{856C6145-2E1C-4B6E-9442-8F25AAAF88C3}" name="القيمة المطلوبة" dataDxfId="1">
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{60C6F871-C16F-4E0C-BCFA-8355ABD999C9}" name="الرقم" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{16663A49-EAEA-4D0C-AEE4-F16F12092E0B}" name="رقم الموظف /رقم البطاقة" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{E695BC9D-90B5-4017-835E-DE39F27EC4B5}" name="اسم المريض" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{4FA0F61B-0974-4290-8AF9-64F3425CF95F}" name="رقم النموذج" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{FA7C7B11-59CD-43FE-8614-AE77C814F7B1}" name="نوع المستفيد" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{A5C7FB1D-369A-430A-90FD-DECEB437BB07}" name="تاريخ البيع" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{A0C6C549-4E6F-40C8-8B90-0D7D85B722AF}" name="قيمة الفاتورة" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{FE5B0B26-736F-4D13-A599-E33B398493F1}" name="قيمة المشاركة" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="9" xr3:uid="{BC1FF825-92ED-4149-A1D2-B9B13F698346}" name="صافي القيمة" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{856C6145-2E1C-4B6E-9442-8F25AAAF88C3}" name="القيمة المطلوبة" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6">
       <calculatedColumnFormula>G2*0.94-H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{93671F58-AEBB-42C2-8ECB-4A20CA480AFD}" name="المدفوع"/>
-    <tableColumn id="12" xr3:uid="{3CB96BCB-F76A-4AB9-8336-BDA8FF662F9F}" name="المتبقي" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{93671F58-AEBB-42C2-8ECB-4A20CA480AFD}" name="المدفوع" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
+      <calculatedColumnFormula>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="12" xr3:uid="{3CB96BCB-F76A-4AB9-8336-BDA8FF662F9F}" name="المتبقي" dataDxfId="3" totalsRowDxfId="2">
       <calculatedColumnFormula>J2-K2</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="13" xr3:uid="{5DF86495-E104-4E7E-9037-241357A5F93D}" name="تاريخ الدفعة" dataDxfId="1" totalsRowDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1277,7 +1489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA9FC926-0A16-40E2-AC7F-885A2855875E}">
-  <dimension ref="A1:L180"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -1289,12 +1501,13 @@
     <col min="7" max="7" width="10.8984375" style="6" customWidth="1"/>
     <col min="8" max="8" width="11.3984375" style="6" customWidth="1"/>
     <col min="9" max="9" width="13.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.19921875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="7.8984375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="6" customWidth="1"/>
+    <col min="11" max="11" width="11.59765625" style="6" customWidth="1"/>
     <col min="12" max="12" width="10.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.69921875" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1331,8 +1544,11 @@
       <c r="L1" s="4" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="M1" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1369,7 +1585,7 @@
         <v>19.984400000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1406,7 +1622,7 @@
         <v>24.778399999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1443,7 +1659,7 @@
         <v>40.814799999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1480,7 +1696,7 @@
         <v>3.4215999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1517,7 +1733,7 @@
         <v>3.6095999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1554,7 +1770,7 @@
         <v>27.184799999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1591,7 +1807,7 @@
         <v>11.482799999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1628,7 +1844,7 @@
         <v>21.092399999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1665,7 +1881,7 @@
         <v>21.335999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1702,7 +1918,7 @@
         <v>11.040799999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1739,7 +1955,7 @@
         <v>9.7901999999999987</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1776,7 +1992,7 @@
         <v>39.723199999999991</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1813,7 +2029,7 @@
         <v>55.943999999999988</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1850,7 +2066,7 @@
         <v>23.293199999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2363,7 +2579,6 @@
         <f t="shared" si="0"/>
         <v>19.9374</v>
       </c>
-      <c r="K29"/>
       <c r="L29" s="6">
         <f t="shared" si="1"/>
         <v>19.9374</v>
@@ -2882,7 +3097,6 @@
         <f t="shared" si="2"/>
         <v>2.3087999999999997</v>
       </c>
-      <c r="K43"/>
       <c r="L43" s="6">
         <f t="shared" si="3"/>
         <v>2.3087999999999997</v>
@@ -3068,7 +3282,6 @@
         <f t="shared" si="2"/>
         <v>18.471599999999995</v>
       </c>
-      <c r="K48"/>
       <c r="L48" s="6">
         <f t="shared" si="3"/>
         <v>18.471599999999995</v>
@@ -3917,7 +4130,6 @@
         <f t="shared" si="4"/>
         <v>10.8262</v>
       </c>
-      <c r="K71"/>
       <c r="L71" s="6">
         <f t="shared" si="5"/>
         <v>10.8262</v>
@@ -4177,7 +4389,6 @@
         <f t="shared" si="4"/>
         <v>19.202399999999997</v>
       </c>
-      <c r="K78"/>
       <c r="L78" s="6">
         <f t="shared" si="5"/>
         <v>19.202399999999997</v>
@@ -5029,7 +5240,6 @@
         <f t="shared" si="6"/>
         <v>17.144399999999997</v>
       </c>
-      <c r="K101"/>
       <c r="L101" s="6">
         <f t="shared" si="7"/>
         <v>17.144399999999997</v>
@@ -5585,7 +5795,6 @@
         <f t="shared" si="6"/>
         <v>8.9459999999999997</v>
       </c>
-      <c r="K116"/>
       <c r="L116" s="6">
         <f t="shared" si="7"/>
         <v>8.9459999999999997</v>
@@ -5623,7 +5832,6 @@
         <f t="shared" si="6"/>
         <v>8.1563999999999997</v>
       </c>
-      <c r="K117"/>
       <c r="L117" s="6">
         <f t="shared" si="7"/>
         <v>8.1563999999999997</v>
@@ -5661,7 +5869,6 @@
         <f t="shared" si="6"/>
         <v>13.692</v>
       </c>
-      <c r="K118"/>
       <c r="L118" s="6">
         <f t="shared" si="7"/>
         <v>13.692</v>
@@ -5699,7 +5906,6 @@
         <f t="shared" si="6"/>
         <v>15.523199999999997</v>
       </c>
-      <c r="K119"/>
       <c r="L119" s="6">
         <f t="shared" si="7"/>
         <v>15.523199999999997</v>
@@ -6144,7 +6350,6 @@
         <f t="shared" si="8"/>
         <v>8.1648000000000014</v>
       </c>
-      <c r="K131"/>
       <c r="L131" s="6">
         <f t="shared" si="9"/>
         <v>8.1648000000000014</v>
@@ -6631,7 +6836,7 @@
         <v>46.695600000000006</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>133</v>
       </c>
@@ -6668,7 +6873,7 @@
         <v>37.884</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>134</v>
       </c>
@@ -6705,7 +6910,7 @@
         <v>4.0889999999999995</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>135</v>
       </c>
@@ -6742,7 +6947,7 @@
         <v>18.705999999999996</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>136</v>
       </c>
@@ -6779,7 +6984,7 @@
         <v>45.444000000000003</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>137</v>
       </c>
@@ -6816,7 +7021,7 @@
         <v>48.118599999999994</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>138</v>
       </c>
@@ -6853,7 +7058,7 @@
         <v>29.349599999999995</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>1</v>
       </c>
@@ -6885,13 +7090,12 @@
         <f t="shared" si="8"/>
         <v>33.599999999999994</v>
       </c>
-      <c r="K151"/>
       <c r="L151" s="6">
         <f t="shared" si="9"/>
         <v>33.599999999999994</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>2</v>
       </c>
@@ -6923,13 +7127,12 @@
         <f t="shared" si="8"/>
         <v>27.325799999999997</v>
       </c>
-      <c r="K152"/>
       <c r="L152" s="6">
         <f t="shared" si="9"/>
         <v>27.325799999999997</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>3</v>
       </c>
@@ -6961,13 +7164,12 @@
         <f t="shared" si="8"/>
         <v>21.907199999999996</v>
       </c>
-      <c r="K153"/>
       <c r="L153" s="6">
         <f t="shared" si="9"/>
         <v>21.907199999999996</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>4</v>
       </c>
@@ -6999,13 +7201,12 @@
         <f t="shared" si="8"/>
         <v>26.1828</v>
       </c>
-      <c r="K154"/>
       <c r="L154" s="6">
         <f t="shared" si="9"/>
         <v>26.1828</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>5</v>
       </c>
@@ -7037,13 +7238,12 @@
         <f t="shared" si="8"/>
         <v>22.6128</v>
       </c>
-      <c r="K155"/>
       <c r="L155" s="6">
         <f t="shared" si="9"/>
         <v>22.6128</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>6</v>
       </c>
@@ -7075,13 +7275,12 @@
         <f t="shared" si="8"/>
         <v>23.387199999999996</v>
       </c>
-      <c r="K156"/>
       <c r="L156" s="6">
         <f t="shared" si="9"/>
         <v>23.387199999999996</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>7</v>
       </c>
@@ -7113,13 +7312,12 @@
         <f t="shared" si="8"/>
         <v>37.447199999999995</v>
       </c>
-      <c r="K157"/>
       <c r="L157" s="6">
         <f t="shared" si="9"/>
         <v>37.447199999999995</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>8</v>
       </c>
@@ -7151,13 +7349,12 @@
         <f t="shared" si="8"/>
         <v>3.7547999999999995</v>
       </c>
-      <c r="K158"/>
       <c r="L158" s="6">
         <f t="shared" si="9"/>
         <v>3.7547999999999995</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>9</v>
       </c>
@@ -7189,13 +7386,12 @@
         <f t="shared" si="8"/>
         <v>40.210799999999999</v>
       </c>
-      <c r="K159"/>
       <c r="L159" s="6">
         <f t="shared" si="9"/>
         <v>40.210799999999999</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>10</v>
       </c>
@@ -7227,13 +7423,19 @@
         <f t="shared" si="8"/>
         <v>21.142800000000001</v>
       </c>
-      <c r="K160"/>
+      <c r="K160" s="6">
+        <f>J160*0.9557</f>
+        <v>20.206173960000001</v>
+      </c>
       <c r="L160" s="6">
         <f t="shared" si="9"/>
-        <v>21.142800000000001</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.93662604000000016</v>
+      </c>
+      <c r="M160" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>11</v>
       </c>
@@ -7265,13 +7467,19 @@
         <f t="shared" si="8"/>
         <v>89.488</v>
       </c>
-      <c r="K161"/>
+      <c r="K161" s="6">
+        <f t="shared" ref="K161:K170" si="10">J161*0.9557</f>
+        <v>85.523681600000003</v>
+      </c>
       <c r="L161" s="6">
         <f t="shared" si="9"/>
-        <v>89.488</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+        <v>3.9643183999999962</v>
+      </c>
+      <c r="M161" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>12</v>
       </c>
@@ -7300,16 +7508,22 @@
         <v>15.48</v>
       </c>
       <c r="J162" s="6">
-        <f t="shared" ref="J162:J174" si="10">G162*0.94-H162</f>
+        <f t="shared" ref="J162:J180" si="11">G162*0.94-H162</f>
         <v>14.447999999999999</v>
       </c>
-      <c r="K162"/>
+      <c r="K162" s="6">
+        <f t="shared" si="10"/>
+        <v>13.807953599999999</v>
+      </c>
       <c r="L162" s="6">
-        <f t="shared" ref="L162:L174" si="11">J162-K162</f>
-        <v>14.447999999999999</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" ref="L162:L193" si="12">J162-K162</f>
+        <v>0.64004639999999924</v>
+      </c>
+      <c r="M162" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>13</v>
       </c>
@@ -7338,15 +7552,22 @@
         <v>40.968000000000004</v>
       </c>
       <c r="J163" s="6">
-        <f t="shared" si="10"/>
-        <v>38.236800000000002</v>
-      </c>
-      <c r="L163" s="6">
         <f t="shared" si="11"/>
         <v>38.236800000000002</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K163" s="6">
+        <f t="shared" si="10"/>
+        <v>36.542909760000001</v>
+      </c>
+      <c r="L163" s="6">
+        <f t="shared" si="12"/>
+        <v>1.6938902400000018</v>
+      </c>
+      <c r="M163" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>14</v>
       </c>
@@ -7375,15 +7596,22 @@
         <v>29.405999999999999</v>
       </c>
       <c r="J164" s="6">
-        <f t="shared" si="10"/>
-        <v>27.445620000000002</v>
-      </c>
-      <c r="L164" s="6">
         <f t="shared" si="11"/>
         <v>27.445620000000002</v>
       </c>
-    </row>
-    <row r="165" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K164" s="6">
+        <f t="shared" si="10"/>
+        <v>26.229779034</v>
+      </c>
+      <c r="L164" s="6">
+        <f t="shared" si="12"/>
+        <v>1.2158409660000018</v>
+      </c>
+      <c r="M164" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>15</v>
       </c>
@@ -7412,15 +7640,22 @@
         <v>6.4980000000000002</v>
       </c>
       <c r="J165" s="6">
-        <f t="shared" si="10"/>
-        <v>6.0648</v>
-      </c>
-      <c r="L165" s="6">
         <f t="shared" si="11"/>
         <v>6.0648</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K165" s="6">
+        <f t="shared" si="10"/>
+        <v>5.7961293600000001</v>
+      </c>
+      <c r="L165" s="6">
+        <f t="shared" si="12"/>
+        <v>0.26867063999999985</v>
+      </c>
+      <c r="M165" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>16</v>
       </c>
@@ -7449,15 +7684,22 @@
         <v>49.805999999999997</v>
       </c>
       <c r="J166" s="6">
-        <f t="shared" si="10"/>
-        <v>46.485599999999998</v>
-      </c>
-      <c r="L166" s="6">
         <f t="shared" si="11"/>
         <v>46.485599999999998</v>
       </c>
-    </row>
-    <row r="167" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K166" s="6">
+        <f t="shared" si="10"/>
+        <v>44.42628792</v>
+      </c>
+      <c r="L166" s="6">
+        <f t="shared" si="12"/>
+        <v>2.059312079999998</v>
+      </c>
+      <c r="M166" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>17</v>
       </c>
@@ -7486,15 +7728,22 @@
         <v>37.368000000000002</v>
       </c>
       <c r="J167" s="6">
-        <f t="shared" si="10"/>
-        <v>34.876800000000003</v>
-      </c>
-      <c r="L167" s="6">
         <f t="shared" si="11"/>
         <v>34.876800000000003</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K167" s="6">
+        <f t="shared" si="10"/>
+        <v>33.331757760000002</v>
+      </c>
+      <c r="L167" s="6">
+        <f t="shared" si="12"/>
+        <v>1.5450422400000008</v>
+      </c>
+      <c r="M167" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>18</v>
       </c>
@@ -7523,15 +7772,22 @@
         <v>31.86</v>
       </c>
       <c r="J168" s="6">
-        <f t="shared" si="10"/>
-        <v>29.735999999999997</v>
-      </c>
-      <c r="L168" s="6">
         <f t="shared" si="11"/>
         <v>29.735999999999997</v>
       </c>
-    </row>
-    <row r="169" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K168" s="6">
+        <f t="shared" si="10"/>
+        <v>28.418695199999998</v>
+      </c>
+      <c r="L168" s="6">
+        <f t="shared" si="12"/>
+        <v>1.3173047999999987</v>
+      </c>
+      <c r="M168" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>19</v>
       </c>
@@ -7560,15 +7816,22 @@
         <v>42.273000000000003</v>
       </c>
       <c r="J169" s="6">
-        <f t="shared" si="10"/>
-        <v>39.454799999999992</v>
-      </c>
-      <c r="L169" s="6">
         <f t="shared" si="11"/>
         <v>39.454799999999992</v>
       </c>
-    </row>
-    <row r="170" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K169" s="6">
+        <f t="shared" si="10"/>
+        <v>37.706952359999988</v>
+      </c>
+      <c r="L169" s="6">
+        <f t="shared" si="12"/>
+        <v>1.7478476400000034</v>
+      </c>
+      <c r="M169" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>20</v>
       </c>
@@ -7597,15 +7860,22 @@
         <v>16.326000000000001</v>
       </c>
       <c r="J170" s="6">
-        <f t="shared" si="10"/>
-        <v>15.2376</v>
-      </c>
-      <c r="L170" s="6">
         <f t="shared" si="11"/>
         <v>15.2376</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K170" s="6">
+        <f t="shared" si="10"/>
+        <v>14.56257432</v>
+      </c>
+      <c r="L170" s="6">
+        <f t="shared" si="12"/>
+        <v>0.67502568000000096</v>
+      </c>
+      <c r="M170" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>1</v>
       </c>
@@ -7634,16 +7904,22 @@
         <v>37.65</v>
       </c>
       <c r="J171" s="6">
-        <f t="shared" si="10"/>
-        <v>35.390999999999998</v>
-      </c>
-      <c r="K171"/>
-      <c r="L171" s="6">
         <f t="shared" si="11"/>
         <v>35.390999999999998</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K171" s="6">
+        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
+        <v>33.8231787</v>
+      </c>
+      <c r="L171" s="6">
+        <f t="shared" si="12"/>
+        <v>1.5678212999999985</v>
+      </c>
+      <c r="M171" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>12</v>
       </c>
@@ -7672,16 +7948,22 @@
         <v>3.4079999999999999</v>
       </c>
       <c r="J172" s="6">
-        <f t="shared" si="10"/>
-        <v>3.1523999999999996</v>
-      </c>
-      <c r="K172"/>
-      <c r="L172" s="6">
         <f t="shared" si="11"/>
         <v>3.1523999999999996</v>
       </c>
-    </row>
-    <row r="173" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K172" s="6">
+        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
+        <v>3.0127486799999996</v>
+      </c>
+      <c r="L172" s="6">
+        <f t="shared" si="12"/>
+        <v>0.13965132000000002</v>
+      </c>
+      <c r="M172" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>2</v>
       </c>
@@ -7710,16 +7992,22 @@
         <v>6.4240000000000004</v>
       </c>
       <c r="J173" s="6">
-        <f t="shared" si="10"/>
-        <v>5.9421999999999988</v>
-      </c>
-      <c r="K173"/>
-      <c r="L173" s="6">
         <f t="shared" si="11"/>
         <v>5.9421999999999988</v>
       </c>
-    </row>
-    <row r="174" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K173" s="6">
+        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
+        <v>5.6789605399999985</v>
+      </c>
+      <c r="L173" s="6">
+        <f t="shared" si="12"/>
+        <v>0.26323946000000031</v>
+      </c>
+      <c r="M173" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>3</v>
       </c>
@@ -7748,16 +8036,22 @@
         <v>40.661999999999999</v>
       </c>
       <c r="J174" s="6">
-        <f t="shared" si="10"/>
-        <v>37.9512</v>
-      </c>
-      <c r="K174"/>
-      <c r="L174" s="6">
         <f t="shared" si="11"/>
         <v>37.9512</v>
       </c>
-    </row>
-    <row r="175" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="K174" s="6">
+        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
+        <v>36.269961840000001</v>
+      </c>
+      <c r="L174" s="6">
+        <f t="shared" si="12"/>
+        <v>1.6812381599999995</v>
+      </c>
+      <c r="M174" s="7">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>1</v>
       </c>
@@ -7786,16 +8080,15 @@
         <v>20.844000000000001</v>
       </c>
       <c r="J175" s="6">
-        <f t="shared" ref="J175:J179" si="12">G175*0.94-H175</f>
+        <f t="shared" si="11"/>
         <v>19.4544</v>
       </c>
-      <c r="K175"/>
       <c r="L175" s="6">
-        <f t="shared" ref="L175:L179" si="13">J175-K175</f>
+        <f t="shared" si="12"/>
         <v>19.4544</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>2</v>
       </c>
@@ -7824,12 +8117,11 @@
         <v>38.780999999999999</v>
       </c>
       <c r="J176" s="6">
+        <f t="shared" si="11"/>
+        <v>36.195600000000006</v>
+      </c>
+      <c r="L176" s="6">
         <f t="shared" si="12"/>
-        <v>36.195600000000006</v>
-      </c>
-      <c r="K176"/>
-      <c r="L176" s="6">
-        <f t="shared" si="13"/>
         <v>36.195600000000006</v>
       </c>
     </row>
@@ -7862,12 +8154,11 @@
         <v>55.552</v>
       </c>
       <c r="J177" s="6">
+        <f t="shared" si="11"/>
+        <v>51.38559999999999</v>
+      </c>
+      <c r="L177" s="6">
         <f t="shared" si="12"/>
-        <v>51.38559999999999</v>
-      </c>
-      <c r="K177"/>
-      <c r="L177" s="6">
-        <f t="shared" si="13"/>
         <v>51.38559999999999</v>
       </c>
     </row>
@@ -7900,89 +8191,105 @@
         <v>34.840000000000003</v>
       </c>
       <c r="J178" s="6">
+        <f t="shared" si="11"/>
+        <v>32.749600000000001</v>
+      </c>
+      <c r="L178" s="6">
         <f t="shared" si="12"/>
         <v>32.749600000000001</v>
       </c>
-      <c r="K178"/>
-      <c r="L178" s="6">
-        <f t="shared" si="13"/>
-        <v>32.749600000000001</v>
-      </c>
     </row>
     <row r="179" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
+        <v>1</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D179" s="2">
+        <v>803592418</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179" s="3">
+        <v>46232</v>
+      </c>
+      <c r="G179" s="2">
+        <v>15.64</v>
+      </c>
+      <c r="H179" s="2">
+        <v>1.5640000000000001</v>
+      </c>
+      <c r="I179" s="2">
+        <v>14.076000000000001</v>
+      </c>
+      <c r="J179" s="6">
+        <f t="shared" si="11"/>
+        <v>13.137599999999999</v>
+      </c>
+      <c r="L179" s="6">
+        <f t="shared" si="12"/>
+        <v>13.137599999999999</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
         <v>5</v>
       </c>
-      <c r="B179" s="2" t="s">
+      <c r="B180" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C179" s="2" t="s">
+      <c r="C180" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D180" s="2">
         <v>803592452</v>
       </c>
-      <c r="E179" s="2" t="s">
+      <c r="E180" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F179" s="3">
+      <c r="F180" s="3">
         <v>46233</v>
       </c>
-      <c r="G179" s="2">
+      <c r="G180" s="2">
         <v>32.56</v>
       </c>
-      <c r="H179" s="2">
+      <c r="H180" s="2">
         <v>3.2559999999999998</v>
       </c>
-      <c r="I179" s="2">
+      <c r="I180" s="2">
         <v>29.303999999999998</v>
       </c>
-      <c r="J179" s="6">
+      <c r="J180" s="6">
+        <f t="shared" si="11"/>
+        <v>27.3504</v>
+      </c>
+      <c r="L180" s="6">
         <f t="shared" si="12"/>
         <v>27.3504</v>
       </c>
-      <c r="K179"/>
-      <c r="L179" s="6">
-        <f t="shared" si="13"/>
-        <v>27.3504</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A180" s="2">
-        <v>1</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D180" s="2">
-        <v>803592418</v>
-      </c>
-      <c r="E180" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F180" s="3">
-        <v>46232</v>
-      </c>
-      <c r="G180" s="2">
-        <v>15.64</v>
-      </c>
-      <c r="H180" s="2">
-        <v>1.5640000000000001</v>
-      </c>
-      <c r="I180" s="2">
-        <v>14.076000000000001</v>
-      </c>
-      <c r="J180" s="6">
-        <f>G180*0.94-H180</f>
-        <v>13.137599999999999</v>
-      </c>
-      <c r="K180"/>
-      <c r="L180" s="6">
-        <f>J180-K180</f>
-        <v>13.137599999999999</v>
+    </row>
+    <row r="181" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="5"/>
+      <c r="H181" s="5"/>
+      <c r="I181" s="5"/>
+      <c r="J181" s="6">
+        <f>SUBTOTAL(109,Table1[القيمة المطلوبة])</f>
+        <v>4324.4574199999997</v>
+      </c>
+      <c r="K181" s="6">
+        <f>SUBTOTAL(109,Table1[المدفوع])</f>
+        <v>425.33774463399999</v>
       </c>
     </row>
   </sheetData>

--- a/ميدسيرفس.xlsx
+++ b/ميدسيرفس.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77164BA9-E866-4FC6-863F-75B6E1AD4A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470A3930-43C1-4966-98CA-0B415DF149B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D788D8F7-2544-4C2F-9B89-70931910278C}"/>
   </bookViews>
@@ -751,21 +751,6 @@
   </cellStyles>
   <dxfs count="27">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -810,6 +795,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -828,6 +814,21 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
@@ -865,7 +866,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="164" formatCode="_-* #,##0.000\ _د_._ا_._‏_-;\-* #,##0.000\ _د_._ا_._‏_-;_-* &quot;-&quot;???\ _د_._ا_._‏_-;_-@_-"/>
     </dxf>
     <dxf>
       <font>
@@ -1154,19 +1154,19 @@
     <tableColumn id="4" xr3:uid="{4FA0F61B-0974-4290-8AF9-64F3425CF95F}" name="رقم النموذج" dataDxfId="19" totalsRowDxfId="18"/>
     <tableColumn id="5" xr3:uid="{FA7C7B11-59CD-43FE-8614-AE77C814F7B1}" name="نوع المستفيد" dataDxfId="17" totalsRowDxfId="16"/>
     <tableColumn id="6" xr3:uid="{A5C7FB1D-369A-430A-90FD-DECEB437BB07}" name="تاريخ البيع" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{A0C6C549-4E6F-40C8-8B90-0D7D85B722AF}" name="قيمة الفاتورة" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{FE5B0B26-736F-4D13-A599-E33B398493F1}" name="قيمة المشاركة" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="9" xr3:uid="{BC1FF825-92ED-4149-A1D2-B9B13F698346}" name="صافي القيمة" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{856C6145-2E1C-4B6E-9442-8F25AAAF88C3}" name="القيمة المطلوبة" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6">
+    <tableColumn id="7" xr3:uid="{A0C6C549-4E6F-40C8-8B90-0D7D85B722AF}" name="قيمة الفاتورة" dataDxfId="13" totalsRowDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{FE5B0B26-736F-4D13-A599-E33B398493F1}" name="قيمة المشاركة" dataDxfId="12" totalsRowDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{BC1FF825-92ED-4149-A1D2-B9B13F698346}" name="صافي القيمة" dataDxfId="11" totalsRowDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{856C6145-2E1C-4B6E-9442-8F25AAAF88C3}" name="القيمة المطلوبة" totalsRowFunction="sum" dataDxfId="10" totalsRowDxfId="2">
       <calculatedColumnFormula>G2*0.94-H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{93671F58-AEBB-42C2-8ECB-4A20CA480AFD}" name="المدفوع" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="11" xr3:uid="{93671F58-AEBB-42C2-8ECB-4A20CA480AFD}" name="المدفوع" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="1">
       <calculatedColumnFormula>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{3CB96BCB-F76A-4AB9-8336-BDA8FF662F9F}" name="المتبقي" dataDxfId="3" totalsRowDxfId="2">
+    <tableColumn id="12" xr3:uid="{3CB96BCB-F76A-4AB9-8336-BDA8FF662F9F}" name="المتبقي" dataDxfId="8" totalsRowDxfId="0">
       <calculatedColumnFormula>J2-K2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{5DF86495-E104-4E7E-9037-241357A5F93D}" name="تاريخ الدفعة" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="13" xr3:uid="{5DF86495-E104-4E7E-9037-241357A5F93D}" name="تاريخ الدفعة" dataDxfId="7" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7516,7 +7516,7 @@
         <v>13.807953599999999</v>
       </c>
       <c r="L162" s="6">
-        <f t="shared" ref="L162:L193" si="12">J162-K162</f>
+        <f t="shared" ref="L162:L180" si="12">J162-K162</f>
         <v>0.64004639999999924</v>
       </c>
       <c r="M162" s="7">
@@ -7916,7 +7916,7 @@
         <v>1.5678212999999985</v>
       </c>
       <c r="M171" s="7">
-        <v>46240</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -7960,7 +7960,7 @@
         <v>0.13965132000000002</v>
       </c>
       <c r="M172" s="7">
-        <v>46240</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -8004,7 +8004,7 @@
         <v>0.26323946000000031</v>
       </c>
       <c r="M173" s="7">
-        <v>46240</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
@@ -8048,7 +8048,7 @@
         <v>1.6812381599999995</v>
       </c>
       <c r="M174" s="7">
-        <v>46240</v>
+        <v>46239</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">

--- a/ميدسيرفس.xlsx
+++ b/ميدسيرفس.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pharmacy_Operations\Insurance_Accounts\Insurance_Claims\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470A3930-43C1-4966-98CA-0B415DF149B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA656969-6837-4DEA-BF58-2FB85178486F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D788D8F7-2544-4C2F-9B89-70931910278C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="221">
   <si>
     <t>الرقم</t>
   </si>
@@ -654,6 +654,51 @@
   </si>
   <si>
     <t>تاريخ الدفعة</t>
+  </si>
+  <si>
+    <t>12997*287184*287248</t>
+  </si>
+  <si>
+    <t>12893*230850*0</t>
+  </si>
+  <si>
+    <t>عبدالله اخميس حسن الحسنات</t>
+  </si>
+  <si>
+    <t>12997*287184*0</t>
+  </si>
+  <si>
+    <t>12885*324758*330803</t>
+  </si>
+  <si>
+    <t>حور عبدالله الحسنات</t>
+  </si>
+  <si>
+    <t>12885*324758*329314</t>
+  </si>
+  <si>
+    <t>منال سليمان النوافلة</t>
+  </si>
+  <si>
+    <t>عزالدين شريف النوافلة</t>
+  </si>
+  <si>
+    <t>مازن خليفة الحمادين</t>
+  </si>
+  <si>
+    <t>فاطمة سليمان القريات</t>
+  </si>
+  <si>
+    <t>12893*231006*304901</t>
+  </si>
+  <si>
+    <t>ترف محمد السبوع</t>
+  </si>
+  <si>
+    <t>12997*287184*287253</t>
+  </si>
+  <si>
+    <t>12893*230886*307697</t>
   </si>
 </sst>
 </file>
@@ -1142,8 +1187,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}" name="Table1" displayName="Table1" ref="A1:M181" totalsRowCount="1" headerRowDxfId="26">
-  <autoFilter ref="A1:M180" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}" name="Table1" displayName="Table1" ref="A1:M195" totalsRowCount="1" headerRowDxfId="26">
+  <autoFilter ref="A1:M194" xr:uid="{0FCAA9DC-BFE0-43FC-AC56-280E1F1086BB}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L180">
     <sortCondition ref="F1:F180"/>
   </sortState>
@@ -1489,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA9FC926-0A16-40E2-AC7F-885A2855875E}">
-  <dimension ref="A1:M181"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.19921875" customWidth="1"/>
@@ -6836,7 +6881,7 @@
         <v>46.695600000000006</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>133</v>
       </c>
@@ -6873,7 +6918,7 @@
         <v>37.884</v>
       </c>
     </row>
-    <row r="146" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>134</v>
       </c>
@@ -6910,7 +6955,7 @@
         <v>4.0889999999999995</v>
       </c>
     </row>
-    <row r="147" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>135</v>
       </c>
@@ -6947,7 +6992,7 @@
         <v>18.705999999999996</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>136</v>
       </c>
@@ -6984,7 +7029,7 @@
         <v>45.444000000000003</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>137</v>
       </c>
@@ -7021,7 +7066,7 @@
         <v>48.118599999999994</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>138</v>
       </c>
@@ -7058,7 +7103,7 @@
         <v>29.349599999999995</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>1</v>
       </c>
@@ -7095,7 +7140,7 @@
         <v>33.599999999999994</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>2</v>
       </c>
@@ -7132,7 +7177,7 @@
         <v>27.325799999999997</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>3</v>
       </c>
@@ -7169,7 +7214,7 @@
         <v>21.907199999999996</v>
       </c>
     </row>
-    <row r="154" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>4</v>
       </c>
@@ -7206,7 +7251,7 @@
         <v>26.1828</v>
       </c>
     </row>
-    <row r="155" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>5</v>
       </c>
@@ -7243,7 +7288,7 @@
         <v>22.6128</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>6</v>
       </c>
@@ -7280,7 +7325,7 @@
         <v>23.387199999999996</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>7</v>
       </c>
@@ -7317,7 +7362,7 @@
         <v>37.447199999999995</v>
       </c>
     </row>
-    <row r="158" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>8</v>
       </c>
@@ -7354,7 +7399,7 @@
         <v>3.7547999999999995</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>9</v>
       </c>
@@ -7391,7 +7436,7 @@
         <v>40.210799999999999</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>10</v>
       </c>
@@ -7423,19 +7468,12 @@
         <f t="shared" si="8"/>
         <v>21.142800000000001</v>
       </c>
-      <c r="K160" s="6">
-        <f>J160*0.9557</f>
-        <v>20.206173960000001</v>
-      </c>
       <c r="L160" s="6">
         <f t="shared" si="9"/>
-        <v>0.93662604000000016</v>
-      </c>
-      <c r="M160" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+        <v>21.142800000000001</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>11</v>
       </c>
@@ -7467,19 +7505,12 @@
         <f t="shared" si="8"/>
         <v>89.488</v>
       </c>
-      <c r="K161" s="6">
-        <f t="shared" ref="K161:K170" si="10">J161*0.9557</f>
-        <v>85.523681600000003</v>
-      </c>
       <c r="L161" s="6">
         <f t="shared" si="9"/>
-        <v>3.9643183999999962</v>
-      </c>
-      <c r="M161" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+        <v>89.488</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>12</v>
       </c>
@@ -7508,22 +7539,15 @@
         <v>15.48</v>
       </c>
       <c r="J162" s="6">
-        <f t="shared" ref="J162:J180" si="11">G162*0.94-H162</f>
+        <f t="shared" ref="J162:J194" si="10">G162*0.94-H162</f>
         <v>14.447999999999999</v>
       </c>
-      <c r="K162" s="6">
-        <f t="shared" si="10"/>
-        <v>13.807953599999999</v>
-      </c>
       <c r="L162" s="6">
-        <f t="shared" ref="L162:L180" si="12">J162-K162</f>
-        <v>0.64004639999999924</v>
-      </c>
-      <c r="M162" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+        <f t="shared" ref="L162:L194" si="11">J162-K162</f>
+        <v>14.447999999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>13</v>
       </c>
@@ -7552,22 +7576,15 @@
         <v>40.968000000000004</v>
       </c>
       <c r="J163" s="6">
+        <f t="shared" si="10"/>
+        <v>38.236800000000002</v>
+      </c>
+      <c r="L163" s="6">
         <f t="shared" si="11"/>
         <v>38.236800000000002</v>
       </c>
-      <c r="K163" s="6">
-        <f t="shared" si="10"/>
-        <v>36.542909760000001</v>
-      </c>
-      <c r="L163" s="6">
-        <f t="shared" si="12"/>
-        <v>1.6938902400000018</v>
-      </c>
-      <c r="M163" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="164" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>14</v>
       </c>
@@ -7596,22 +7613,15 @@
         <v>29.405999999999999</v>
       </c>
       <c r="J164" s="6">
+        <f t="shared" si="10"/>
+        <v>27.445620000000002</v>
+      </c>
+      <c r="L164" s="6">
         <f t="shared" si="11"/>
         <v>27.445620000000002</v>
       </c>
-      <c r="K164" s="6">
-        <f t="shared" si="10"/>
-        <v>26.229779034</v>
-      </c>
-      <c r="L164" s="6">
-        <f t="shared" si="12"/>
-        <v>1.2158409660000018</v>
-      </c>
-      <c r="M164" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="165" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>15</v>
       </c>
@@ -7640,22 +7650,15 @@
         <v>6.4980000000000002</v>
       </c>
       <c r="J165" s="6">
+        <f t="shared" si="10"/>
+        <v>6.0648</v>
+      </c>
+      <c r="L165" s="6">
         <f t="shared" si="11"/>
         <v>6.0648</v>
       </c>
-      <c r="K165" s="6">
-        <f t="shared" si="10"/>
-        <v>5.7961293600000001</v>
-      </c>
-      <c r="L165" s="6">
-        <f t="shared" si="12"/>
-        <v>0.26867063999999985</v>
-      </c>
-      <c r="M165" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="166" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>16</v>
       </c>
@@ -7684,22 +7687,15 @@
         <v>49.805999999999997</v>
       </c>
       <c r="J166" s="6">
+        <f t="shared" si="10"/>
+        <v>46.485599999999998</v>
+      </c>
+      <c r="L166" s="6">
         <f t="shared" si="11"/>
         <v>46.485599999999998</v>
       </c>
-      <c r="K166" s="6">
-        <f t="shared" si="10"/>
-        <v>44.42628792</v>
-      </c>
-      <c r="L166" s="6">
-        <f t="shared" si="12"/>
-        <v>2.059312079999998</v>
-      </c>
-      <c r="M166" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="167" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>17</v>
       </c>
@@ -7728,22 +7724,15 @@
         <v>37.368000000000002</v>
       </c>
       <c r="J167" s="6">
+        <f t="shared" si="10"/>
+        <v>34.876800000000003</v>
+      </c>
+      <c r="L167" s="6">
         <f t="shared" si="11"/>
         <v>34.876800000000003</v>
       </c>
-      <c r="K167" s="6">
-        <f t="shared" si="10"/>
-        <v>33.331757760000002</v>
-      </c>
-      <c r="L167" s="6">
-        <f t="shared" si="12"/>
-        <v>1.5450422400000008</v>
-      </c>
-      <c r="M167" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="168" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="168" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>18</v>
       </c>
@@ -7772,22 +7761,15 @@
         <v>31.86</v>
       </c>
       <c r="J168" s="6">
+        <f t="shared" si="10"/>
+        <v>29.735999999999997</v>
+      </c>
+      <c r="L168" s="6">
         <f t="shared" si="11"/>
         <v>29.735999999999997</v>
       </c>
-      <c r="K168" s="6">
-        <f t="shared" si="10"/>
-        <v>28.418695199999998</v>
-      </c>
-      <c r="L168" s="6">
-        <f t="shared" si="12"/>
-        <v>1.3173047999999987</v>
-      </c>
-      <c r="M168" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="169" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>19</v>
       </c>
@@ -7816,22 +7798,15 @@
         <v>42.273000000000003</v>
       </c>
       <c r="J169" s="6">
+        <f t="shared" si="10"/>
+        <v>39.454799999999992</v>
+      </c>
+      <c r="L169" s="6">
         <f t="shared" si="11"/>
         <v>39.454799999999992</v>
       </c>
-      <c r="K169" s="6">
-        <f t="shared" si="10"/>
-        <v>37.706952359999988</v>
-      </c>
-      <c r="L169" s="6">
-        <f t="shared" si="12"/>
-        <v>1.7478476400000034</v>
-      </c>
-      <c r="M169" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="170" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>20</v>
       </c>
@@ -7860,22 +7835,15 @@
         <v>16.326000000000001</v>
       </c>
       <c r="J170" s="6">
+        <f t="shared" si="10"/>
+        <v>15.2376</v>
+      </c>
+      <c r="L170" s="6">
         <f t="shared" si="11"/>
         <v>15.2376</v>
       </c>
-      <c r="K170" s="6">
-        <f t="shared" si="10"/>
-        <v>14.56257432</v>
-      </c>
-      <c r="L170" s="6">
-        <f t="shared" si="12"/>
-        <v>0.67502568000000096</v>
-      </c>
-      <c r="M170" s="7">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="171" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>1</v>
       </c>
@@ -7904,22 +7872,15 @@
         <v>37.65</v>
       </c>
       <c r="J171" s="6">
+        <f t="shared" si="10"/>
+        <v>35.390999999999998</v>
+      </c>
+      <c r="L171" s="6">
         <f t="shared" si="11"/>
         <v>35.390999999999998</v>
       </c>
-      <c r="K171" s="6">
-        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
-        <v>33.8231787</v>
-      </c>
-      <c r="L171" s="6">
-        <f t="shared" si="12"/>
-        <v>1.5678212999999985</v>
-      </c>
-      <c r="M171" s="7">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="172" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>12</v>
       </c>
@@ -7948,22 +7909,15 @@
         <v>3.4079999999999999</v>
       </c>
       <c r="J172" s="6">
+        <f t="shared" si="10"/>
+        <v>3.1523999999999996</v>
+      </c>
+      <c r="L172" s="6">
         <f t="shared" si="11"/>
         <v>3.1523999999999996</v>
       </c>
-      <c r="K172" s="6">
-        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
-        <v>3.0127486799999996</v>
-      </c>
-      <c r="L172" s="6">
-        <f t="shared" si="12"/>
-        <v>0.13965132000000002</v>
-      </c>
-      <c r="M172" s="7">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="173" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>2</v>
       </c>
@@ -7992,22 +7946,15 @@
         <v>6.4240000000000004</v>
       </c>
       <c r="J173" s="6">
+        <f t="shared" si="10"/>
+        <v>5.9421999999999988</v>
+      </c>
+      <c r="L173" s="6">
         <f t="shared" si="11"/>
         <v>5.9421999999999988</v>
       </c>
-      <c r="K173" s="6">
-        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
-        <v>5.6789605399999985</v>
-      </c>
-      <c r="L173" s="6">
-        <f t="shared" si="12"/>
-        <v>0.26323946000000031</v>
-      </c>
-      <c r="M173" s="7">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="174" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="174" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>3</v>
       </c>
@@ -8036,22 +7983,15 @@
         <v>40.661999999999999</v>
       </c>
       <c r="J174" s="6">
+        <f t="shared" si="10"/>
+        <v>37.9512</v>
+      </c>
+      <c r="L174" s="6">
         <f t="shared" si="11"/>
         <v>37.9512</v>
       </c>
-      <c r="K174" s="6">
-        <f>Table1[[#This Row],[القيمة المطلوبة]]*0.9557</f>
-        <v>36.269961840000001</v>
-      </c>
-      <c r="L174" s="6">
-        <f t="shared" si="12"/>
-        <v>1.6812381599999995</v>
-      </c>
-      <c r="M174" s="7">
-        <v>46239</v>
-      </c>
-    </row>
-    <row r="175" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="175" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>1</v>
       </c>
@@ -8080,15 +8020,15 @@
         <v>20.844000000000001</v>
       </c>
       <c r="J175" s="6">
+        <f t="shared" si="10"/>
+        <v>19.4544</v>
+      </c>
+      <c r="L175" s="6">
         <f t="shared" si="11"/>
         <v>19.4544</v>
       </c>
-      <c r="L175" s="6">
-        <f t="shared" si="12"/>
-        <v>19.4544</v>
-      </c>
-    </row>
-    <row r="176" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="176" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>2</v>
       </c>
@@ -8117,15 +8057,15 @@
         <v>38.780999999999999</v>
       </c>
       <c r="J176" s="6">
+        <f t="shared" si="10"/>
+        <v>36.195600000000006</v>
+      </c>
+      <c r="L176" s="6">
         <f t="shared" si="11"/>
         <v>36.195600000000006</v>
       </c>
-      <c r="L176" s="6">
-        <f t="shared" si="12"/>
-        <v>36.195600000000006</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="177" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>3</v>
       </c>
@@ -8154,15 +8094,15 @@
         <v>55.552</v>
       </c>
       <c r="J177" s="6">
+        <f t="shared" si="10"/>
+        <v>51.38559999999999</v>
+      </c>
+      <c r="L177" s="6">
         <f t="shared" si="11"/>
         <v>51.38559999999999</v>
       </c>
-      <c r="L177" s="6">
-        <f t="shared" si="12"/>
-        <v>51.38559999999999</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="178" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>4</v>
       </c>
@@ -8191,15 +8131,15 @@
         <v>34.840000000000003</v>
       </c>
       <c r="J178" s="6">
+        <f t="shared" si="10"/>
+        <v>32.749600000000001</v>
+      </c>
+      <c r="L178" s="6">
         <f t="shared" si="11"/>
         <v>32.749600000000001</v>
       </c>
-      <c r="L178" s="6">
-        <f t="shared" si="12"/>
-        <v>32.749600000000001</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>1</v>
       </c>
@@ -8228,15 +8168,15 @@
         <v>14.076000000000001</v>
       </c>
       <c r="J179" s="6">
+        <f t="shared" si="10"/>
+        <v>13.137599999999999</v>
+      </c>
+      <c r="L179" s="6">
         <f t="shared" si="11"/>
         <v>13.137599999999999</v>
       </c>
-      <c r="L179" s="6">
-        <f t="shared" si="12"/>
-        <v>13.137599999999999</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="180" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>5</v>
       </c>
@@ -8265,31 +8205,577 @@
         <v>29.303999999999998</v>
       </c>
       <c r="J180" s="6">
+        <f t="shared" si="10"/>
+        <v>27.3504</v>
+      </c>
+      <c r="L180" s="6">
         <f t="shared" si="11"/>
         <v>27.3504</v>
       </c>
-      <c r="L180" s="6">
-        <f t="shared" si="12"/>
-        <v>27.3504</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A181" s="2"/>
-      <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
-      <c r="E181" s="2"/>
-      <c r="F181" s="3"/>
-      <c r="G181" s="5"/>
-      <c r="H181" s="5"/>
-      <c r="I181" s="5"/>
+    </row>
+    <row r="181" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A181" s="2">
+        <v>1</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D181" s="2">
+        <v>803596805</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F181" s="3">
+        <v>46235</v>
+      </c>
+      <c r="G181" s="2">
+        <v>44.95</v>
+      </c>
+      <c r="H181" s="2">
+        <v>4.4950000000000001</v>
+      </c>
+      <c r="I181" s="2">
+        <v>40.454999999999998</v>
+      </c>
       <c r="J181" s="6">
+        <f t="shared" si="10"/>
+        <v>37.758000000000003</v>
+      </c>
+      <c r="K181"/>
+      <c r="L181" s="6">
+        <f t="shared" si="11"/>
+        <v>37.758000000000003</v>
+      </c>
+      <c r="M181"/>
+    </row>
+    <row r="182" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A182" s="2">
+        <v>2</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D182" s="2">
+        <v>803597807</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F182" s="3">
+        <v>46238</v>
+      </c>
+      <c r="G182" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="H182" s="2">
+        <v>0</v>
+      </c>
+      <c r="I182" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="J182" s="6">
+        <f t="shared" si="10"/>
+        <v>14.805</v>
+      </c>
+      <c r="K182"/>
+      <c r="L182" s="6">
+        <f t="shared" si="11"/>
+        <v>14.805</v>
+      </c>
+      <c r="M182"/>
+    </row>
+    <row r="183" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A183" s="2">
+        <v>3</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D183" s="2">
+        <v>803596629</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F183" s="3">
+        <v>46240</v>
+      </c>
+      <c r="G183" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="H183" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="I183" s="2">
+        <v>6.75</v>
+      </c>
+      <c r="J183" s="6">
+        <f t="shared" si="10"/>
+        <v>6.3</v>
+      </c>
+      <c r="K183"/>
+      <c r="L183" s="6">
+        <f t="shared" si="11"/>
+        <v>6.3</v>
+      </c>
+      <c r="M183"/>
+    </row>
+    <row r="184" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
+        <v>4</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D184" s="2">
+        <v>803598372</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F184" s="3">
+        <v>46241</v>
+      </c>
+      <c r="G184" s="2">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="H184" s="2">
+        <v>0</v>
+      </c>
+      <c r="I184" s="2">
+        <v>8.9600000000000009</v>
+      </c>
+      <c r="J184" s="6">
+        <f t="shared" si="10"/>
+        <v>8.4223999999999997</v>
+      </c>
+      <c r="K184"/>
+      <c r="L184" s="6">
+        <f t="shared" si="11"/>
+        <v>8.4223999999999997</v>
+      </c>
+      <c r="M184"/>
+    </row>
+    <row r="185" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A185" s="2">
+        <v>5</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D185" s="2">
+        <v>803598815</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F185" s="3">
+        <v>46242</v>
+      </c>
+      <c r="G185" s="2">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="H185" s="2">
+        <v>1.9059999999999999</v>
+      </c>
+      <c r="I185" s="2">
+        <v>7.6239999999999997</v>
+      </c>
+      <c r="J185" s="6">
+        <f t="shared" si="10"/>
+        <v>7.0522</v>
+      </c>
+      <c r="K185"/>
+      <c r="L185" s="6">
+        <f t="shared" si="11"/>
+        <v>7.0522</v>
+      </c>
+      <c r="M185"/>
+    </row>
+    <row r="186" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A186" s="2">
+        <v>6</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D186" s="2">
+        <v>803598818</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F186" s="3">
+        <v>46242</v>
+      </c>
+      <c r="G186" s="2">
+        <v>59.83</v>
+      </c>
+      <c r="H186" s="2">
+        <v>11.965999999999999</v>
+      </c>
+      <c r="I186" s="2">
+        <v>47.863999999999997</v>
+      </c>
+      <c r="J186" s="6">
+        <f t="shared" si="10"/>
+        <v>44.274199999999993</v>
+      </c>
+      <c r="K186"/>
+      <c r="L186" s="6">
+        <f t="shared" si="11"/>
+        <v>44.274199999999993</v>
+      </c>
+      <c r="M186"/>
+    </row>
+    <row r="187" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A187" s="2">
+        <v>7</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D187" s="2">
+        <v>803599722</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F187" s="3">
+        <v>46245</v>
+      </c>
+      <c r="G187" s="2">
+        <v>35.67</v>
+      </c>
+      <c r="H187" s="2">
+        <v>3.5670000000000002</v>
+      </c>
+      <c r="I187" s="2">
+        <v>32.103000000000002</v>
+      </c>
+      <c r="J187" s="6">
+        <f t="shared" si="10"/>
+        <v>29.962800000000001</v>
+      </c>
+      <c r="K187"/>
+      <c r="L187" s="6">
+        <f t="shared" si="11"/>
+        <v>29.962800000000001</v>
+      </c>
+      <c r="M187"/>
+    </row>
+    <row r="188" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A188" s="2">
+        <v>8</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D188" s="2">
+        <v>803599721</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F188" s="3">
+        <v>46245</v>
+      </c>
+      <c r="G188" s="2">
+        <v>21.86</v>
+      </c>
+      <c r="H188" s="2">
+        <v>2.1859999999999999</v>
+      </c>
+      <c r="I188" s="2">
+        <v>19.673999999999999</v>
+      </c>
+      <c r="J188" s="6">
+        <f t="shared" si="10"/>
+        <v>18.362399999999997</v>
+      </c>
+      <c r="K188"/>
+      <c r="L188" s="6">
+        <f t="shared" si="11"/>
+        <v>18.362399999999997</v>
+      </c>
+      <c r="M188"/>
+    </row>
+    <row r="189" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A189" s="2">
+        <v>9</v>
+      </c>
+      <c r="B189" s="2">
+        <v>284960</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D189" s="2">
+        <v>803600048</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F189" s="3">
+        <v>46246</v>
+      </c>
+      <c r="G189" s="2">
+        <v>6.64</v>
+      </c>
+      <c r="H189" s="2">
+        <v>1.3280000000000001</v>
+      </c>
+      <c r="I189" s="2">
+        <v>5.3120000000000003</v>
+      </c>
+      <c r="J189" s="6">
+        <f t="shared" si="10"/>
+        <v>4.9135999999999989</v>
+      </c>
+      <c r="K189"/>
+      <c r="L189" s="6">
+        <f t="shared" si="11"/>
+        <v>4.9135999999999989</v>
+      </c>
+      <c r="M189"/>
+    </row>
+    <row r="190" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A190" s="2">
+        <v>10</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D190" s="2">
+        <v>803602382</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F190" s="3">
+        <v>46255</v>
+      </c>
+      <c r="G190" s="2">
+        <v>9.07</v>
+      </c>
+      <c r="H190" s="2">
+        <v>0.90700000000000003</v>
+      </c>
+      <c r="I190" s="2">
+        <v>8.1630000000000003</v>
+      </c>
+      <c r="J190" s="6">
+        <f t="shared" si="10"/>
+        <v>7.6188000000000002</v>
+      </c>
+      <c r="K190"/>
+      <c r="L190" s="6">
+        <f t="shared" si="11"/>
+        <v>7.6188000000000002</v>
+      </c>
+      <c r="M190"/>
+    </row>
+    <row r="191" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A191" s="2">
+        <v>11</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D191" s="2">
+        <v>803602380</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" s="3">
+        <v>46255</v>
+      </c>
+      <c r="G191" s="2">
+        <v>4.38</v>
+      </c>
+      <c r="H191" s="2">
+        <v>0.438</v>
+      </c>
+      <c r="I191" s="2">
+        <v>3.9420000000000002</v>
+      </c>
+      <c r="J191" s="6">
+        <f t="shared" si="10"/>
+        <v>3.6791999999999994</v>
+      </c>
+      <c r="K191"/>
+      <c r="L191" s="6">
+        <f t="shared" si="11"/>
+        <v>3.6791999999999994</v>
+      </c>
+      <c r="M191"/>
+    </row>
+    <row r="192" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A192" s="2">
+        <v>12</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D192" s="2">
+        <v>803602393</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F192" s="3">
+        <v>46259</v>
+      </c>
+      <c r="G192" s="2">
+        <v>24</v>
+      </c>
+      <c r="H192" s="2">
+        <v>0</v>
+      </c>
+      <c r="I192" s="2">
+        <v>24</v>
+      </c>
+      <c r="J192" s="6">
+        <f t="shared" si="10"/>
+        <v>22.56</v>
+      </c>
+      <c r="K192"/>
+      <c r="L192" s="6">
+        <f t="shared" si="11"/>
+        <v>22.56</v>
+      </c>
+      <c r="M192"/>
+    </row>
+    <row r="193" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A193" s="2">
+        <v>13</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D193" s="2">
+        <v>803600240</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F193" s="3">
+        <v>46264</v>
+      </c>
+      <c r="G193" s="2">
+        <v>49.27</v>
+      </c>
+      <c r="H193" s="2">
+        <v>4.9269999999999996</v>
+      </c>
+      <c r="I193" s="2">
+        <v>44.343000000000004</v>
+      </c>
+      <c r="J193" s="6">
+        <f t="shared" si="10"/>
+        <v>41.386800000000001</v>
+      </c>
+      <c r="K193"/>
+      <c r="L193" s="6">
+        <f t="shared" si="11"/>
+        <v>41.386800000000001</v>
+      </c>
+      <c r="M193"/>
+    </row>
+    <row r="194" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A194" s="2">
+        <v>14</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D194" s="2">
+        <v>803600239</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F194" s="3">
+        <v>46264</v>
+      </c>
+      <c r="G194" s="2">
+        <v>39.17</v>
+      </c>
+      <c r="H194" s="2">
+        <v>3.9169999999999998</v>
+      </c>
+      <c r="I194" s="2">
+        <v>35.253</v>
+      </c>
+      <c r="J194" s="6">
+        <f t="shared" si="10"/>
+        <v>32.902799999999999</v>
+      </c>
+      <c r="K194"/>
+      <c r="L194" s="6">
+        <f t="shared" si="11"/>
+        <v>32.902799999999999</v>
+      </c>
+      <c r="M194"/>
+    </row>
+    <row r="195" spans="1:13" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A195" s="2"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="2"/>
+      <c r="F195" s="3"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5"/>
+      <c r="J195" s="6">
         <f>SUBTOTAL(109,Table1[القيمة المطلوبة])</f>
-        <v>4324.4574199999997</v>
-      </c>
-      <c r="K181" s="6">
+        <v>4604.4556200000006</v>
+      </c>
+      <c r="K195" s="6">
         <f>SUBTOTAL(109,Table1[المدفوع])</f>
-        <v>425.33774463399999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
